--- a/0_SELECT_ZIVE_DATA_2023/visi_zive_irasai_atrankai._modif_v1 - Darb.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/visi_zive_irasai_atrankai._modif_v1 - Darb.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\1_PREPARE_TRAIN_UNET_DATA\ScriptsForAnalysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907D382E-C09C-4E0F-A8DB-881702D19AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C7EE8B-34AD-478A-BB13-CF88B203A233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12167,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -12246,7 +12246,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -12328,7 +12328,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -12405,13 +12405,13 @@
         <v>4</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -12484,10 +12484,10 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -12563,7 +12563,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -12642,13 +12642,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -12724,7 +12724,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -12809,7 +12809,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -12882,7 +12882,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -13037,10 +13037,10 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -13116,10 +13116,10 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -13195,10 +13195,10 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -13277,7 +13277,7 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -13353,10 +13353,10 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -13432,10 +13432,10 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -13514,7 +13514,7 @@
         <v>0</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -13748,7 +13748,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -13827,7 +13827,7 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -13982,7 +13982,7 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -14061,7 +14061,7 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -14219,7 +14219,7 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -14298,7 +14298,7 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -14374,7 +14374,7 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -14453,7 +14453,7 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -14611,7 +14611,7 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -14766,7 +14766,7 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -14845,7 +14845,7 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -14927,10 +14927,10 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -15006,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -15085,10 +15085,10 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -15164,7 +15164,7 @@
         <v>0</v>
       </c>
       <c r="N40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -15243,7 +15243,7 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -15319,7 +15319,7 @@
         <v>0</v>
       </c>
       <c r="N42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -15398,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="O43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -15480,7 +15480,7 @@
         <v>0</v>
       </c>
       <c r="O44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44">
         <v>0</v>
@@ -15556,7 +15556,7 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -15714,7 +15714,7 @@
         <v>0</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -15878,10 +15878,10 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -15957,10 +15957,10 @@
         <v>0</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -16036,10 +16036,10 @@
         <v>0</v>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -16118,7 +16118,7 @@
         <v>0</v>
       </c>
       <c r="O52">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -16197,10 +16197,10 @@
         <v>0</v>
       </c>
       <c r="N53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -16279,10 +16279,10 @@
         <v>0</v>
       </c>
       <c r="O54">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -16358,7 +16358,7 @@
         <v>0</v>
       </c>
       <c r="O55">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -16437,7 +16437,7 @@
         <v>0</v>
       </c>
       <c r="O56">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -16516,7 +16516,7 @@
         <v>0</v>
       </c>
       <c r="O57">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -16595,10 +16595,10 @@
         <v>0</v>
       </c>
       <c r="O58">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="O59">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -16747,10 +16747,10 @@
         <v>0</v>
       </c>
       <c r="O60">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -16826,7 +16826,7 @@
         <v>0</v>
       </c>
       <c r="O61">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -16905,7 +16905,7 @@
         <v>0</v>
       </c>
       <c r="O62">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -16984,7 +16984,7 @@
         <v>0</v>
       </c>
       <c r="O63">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -17063,7 +17063,7 @@
         <v>0</v>
       </c>
       <c r="O64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -17142,7 +17142,7 @@
         <v>0</v>
       </c>
       <c r="O65">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -17221,7 +17221,7 @@
         <v>0</v>
       </c>
       <c r="O66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66">
         <v>0</v>
@@ -17297,10 +17297,10 @@
         <v>0</v>
       </c>
       <c r="N67">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P67">
         <v>0</v>
@@ -17376,10 +17376,10 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P68">
         <v>0</v>
@@ -17458,7 +17458,7 @@
         <v>0</v>
       </c>
       <c r="O69">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P69">
         <v>0</v>
@@ -17534,10 +17534,10 @@
         <v>0</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P70">
         <v>0</v>
@@ -17613,10 +17613,10 @@
         <v>0</v>
       </c>
       <c r="N71">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P71">
         <v>0</v>
@@ -17692,10 +17692,10 @@
         <v>0</v>
       </c>
       <c r="N72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P72">
         <v>0</v>
@@ -17768,10 +17768,10 @@
         <v>0</v>
       </c>
       <c r="N73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P73">
         <v>0</v>
@@ -17847,7 +17847,7 @@
         <v>0</v>
       </c>
       <c r="N74">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -17923,7 +17923,7 @@
         <v>0</v>
       </c>
       <c r="N75">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -18002,7 +18002,7 @@
         <v>0</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -18081,7 +18081,7 @@
         <v>0</v>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="N78">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -18245,7 +18245,7 @@
         <v>0</v>
       </c>
       <c r="N79">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -18324,7 +18324,7 @@
         <v>0</v>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -18403,7 +18403,7 @@
         <v>0</v>
       </c>
       <c r="N81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -18482,7 +18482,7 @@
         <v>0</v>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -18561,7 +18561,7 @@
         <v>0</v>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -18640,7 +18640,7 @@
         <v>0</v>
       </c>
       <c r="N84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -18719,7 +18719,7 @@
         <v>0</v>
       </c>
       <c r="N85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -18798,13 +18798,13 @@
         <v>5</v>
       </c>
       <c r="N86">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O86">
         <v>0</v>
       </c>
       <c r="P86">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -18877,7 +18877,7 @@
         <v>0</v>
       </c>
       <c r="N87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -18956,7 +18956,7 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -19035,7 +19035,7 @@
         <v>0</v>
       </c>
       <c r="N89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -19114,7 +19114,7 @@
         <v>0</v>
       </c>
       <c r="N90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -19193,7 +19193,7 @@
         <v>0</v>
       </c>
       <c r="N91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -19272,7 +19272,7 @@
         <v>0</v>
       </c>
       <c r="N92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -19351,7 +19351,7 @@
         <v>0</v>
       </c>
       <c r="N93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -19430,7 +19430,7 @@
         <v>0</v>
       </c>
       <c r="N94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -19588,7 +19588,7 @@
         <v>0</v>
       </c>
       <c r="N96">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -19667,7 +19667,7 @@
         <v>0</v>
       </c>
       <c r="N97">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -19746,7 +19746,7 @@
         <v>0</v>
       </c>
       <c r="N98">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -19825,7 +19825,7 @@
         <v>0</v>
       </c>
       <c r="N99">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -19904,7 +19904,7 @@
         <v>0</v>
       </c>
       <c r="N100">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -19983,7 +19983,7 @@
         <v>0</v>
       </c>
       <c r="N101">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -20062,7 +20062,7 @@
         <v>0</v>
       </c>
       <c r="N102">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -20144,7 +20144,7 @@
         <v>0</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -20308,7 +20308,7 @@
         <v>0</v>
       </c>
       <c r="O105">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P105">
         <v>0</v>
@@ -20387,7 +20387,7 @@
         <v>0</v>
       </c>
       <c r="N106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -20545,10 +20545,10 @@
         <v>0</v>
       </c>
       <c r="N108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P108">
         <v>0</v>
@@ -20624,7 +20624,7 @@
         <v>0</v>
       </c>
       <c r="N109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -20703,7 +20703,7 @@
         <v>0</v>
       </c>
       <c r="N110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -20785,7 +20785,7 @@
         <v>0</v>
       </c>
       <c r="O111">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="P111">
         <v>0</v>
@@ -20864,7 +20864,7 @@
         <v>0</v>
       </c>
       <c r="O112">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -20943,7 +20943,7 @@
         <v>0</v>
       </c>
       <c r="O113">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="P113">
         <v>0</v>
@@ -21022,7 +21022,7 @@
         <v>0</v>
       </c>
       <c r="O114">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="P114">
         <v>0</v>
@@ -21101,7 +21101,7 @@
         <v>0</v>
       </c>
       <c r="O115">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="P115">
         <v>0</v>
@@ -21183,7 +21183,7 @@
         <v>0</v>
       </c>
       <c r="O116">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="P116">
         <v>0</v>
@@ -21265,7 +21265,7 @@
         <v>0</v>
       </c>
       <c r="O117">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="P117">
         <v>0</v>
@@ -21344,7 +21344,7 @@
         <v>0</v>
       </c>
       <c r="O118">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -21423,7 +21423,7 @@
         <v>0</v>
       </c>
       <c r="O119">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -21502,7 +21502,7 @@
         <v>0</v>
       </c>
       <c r="O120">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -21581,7 +21581,7 @@
         <v>0</v>
       </c>
       <c r="O121">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="P121">
         <v>0</v>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="O122">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -21739,7 +21739,7 @@
         <v>0</v>
       </c>
       <c r="O123">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="P123">
         <v>0</v>
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="O124">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="P124">
         <v>0</v>
@@ -21897,7 +21897,7 @@
         <v>0</v>
       </c>
       <c r="O125">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P125">
         <v>0</v>
@@ -21976,7 +21976,7 @@
         <v>0</v>
       </c>
       <c r="O126">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P126">
         <v>0</v>
@@ -22055,7 +22055,7 @@
         <v>0</v>
       </c>
       <c r="O127">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="P127">
         <v>0</v>
@@ -22134,7 +22134,7 @@
         <v>0</v>
       </c>
       <c r="O128">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P128">
         <v>0</v>
@@ -22213,7 +22213,7 @@
         <v>0</v>
       </c>
       <c r="O129">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P129">
         <v>0</v>
@@ -22292,7 +22292,7 @@
         <v>0</v>
       </c>
       <c r="O130">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P130">
         <v>0</v>
@@ -22371,7 +22371,7 @@
         <v>0</v>
       </c>
       <c r="O131">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P131">
         <v>0</v>
@@ -22450,7 +22450,7 @@
         <v>0</v>
       </c>
       <c r="O132">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P132">
         <v>0</v>
@@ -22526,7 +22526,7 @@
         <v>0</v>
       </c>
       <c r="O133">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P133">
         <v>0</v>
@@ -22605,7 +22605,7 @@
         <v>0</v>
       </c>
       <c r="O134">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="P134">
         <v>0</v>
@@ -22684,7 +22684,7 @@
         <v>0</v>
       </c>
       <c r="O135">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P135">
         <v>0</v>
@@ -22763,7 +22763,7 @@
         <v>0</v>
       </c>
       <c r="O136">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P136">
         <v>0</v>
@@ -22842,7 +22842,7 @@
         <v>0</v>
       </c>
       <c r="O137">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P137">
         <v>0</v>
@@ -22921,7 +22921,7 @@
         <v>0</v>
       </c>
       <c r="O138">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P138">
         <v>0</v>
@@ -23000,7 +23000,7 @@
         <v>0</v>
       </c>
       <c r="O139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P139">
         <v>0</v>
@@ -23079,7 +23079,7 @@
         <v>0</v>
       </c>
       <c r="O140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P140">
         <v>0</v>
@@ -23155,10 +23155,10 @@
         <v>0</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P141">
         <v>0</v>
@@ -23237,7 +23237,7 @@
         <v>0</v>
       </c>
       <c r="O142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P142">
         <v>0</v>
@@ -23313,7 +23313,7 @@
         <v>0</v>
       </c>
       <c r="N143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>0</v>
       </c>
       <c r="O144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P144">
         <v>0</v>
@@ -23474,7 +23474,7 @@
         <v>0</v>
       </c>
       <c r="O145">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="P145">
         <v>0</v>
@@ -23632,7 +23632,7 @@
         <v>0</v>
       </c>
       <c r="O147">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="P147">
         <v>0</v>
@@ -23711,7 +23711,7 @@
         <v>0</v>
       </c>
       <c r="O148">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="P148">
         <v>0</v>
@@ -23790,7 +23790,7 @@
         <v>0</v>
       </c>
       <c r="O149">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="P149">
         <v>0</v>
@@ -23869,7 +23869,7 @@
         <v>0</v>
       </c>
       <c r="O150">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="P150">
         <v>0</v>
@@ -23948,7 +23948,7 @@
         <v>0</v>
       </c>
       <c r="O151">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="P151">
         <v>0</v>
@@ -24109,7 +24109,7 @@
         <v>0</v>
       </c>
       <c r="O153">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="P153">
         <v>0</v>
@@ -24188,7 +24188,7 @@
         <v>0</v>
       </c>
       <c r="O154">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="P154">
         <v>0</v>
@@ -24264,7 +24264,7 @@
         <v>0</v>
       </c>
       <c r="O155">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P155">
         <v>0</v>
@@ -24343,7 +24343,7 @@
         <v>0</v>
       </c>
       <c r="O156">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P156">
         <v>0</v>
@@ -24422,7 +24422,7 @@
         <v>0</v>
       </c>
       <c r="O157">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="P157">
         <v>0</v>
@@ -24501,7 +24501,7 @@
         <v>0</v>
       </c>
       <c r="O158">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="P158">
         <v>0</v>
@@ -24580,7 +24580,7 @@
         <v>0</v>
       </c>
       <c r="O159">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="P159">
         <v>0</v>
@@ -24659,7 +24659,7 @@
         <v>0</v>
       </c>
       <c r="O160">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P160">
         <v>0</v>
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="O161">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P161">
         <v>0</v>
@@ -24820,7 +24820,7 @@
         <v>0</v>
       </c>
       <c r="O162">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P162">
         <v>0</v>
@@ -24899,7 +24899,7 @@
         <v>0</v>
       </c>
       <c r="O163">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P163">
         <v>0</v>
@@ -24978,7 +24978,7 @@
         <v>0</v>
       </c>
       <c r="O164">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P164">
         <v>0</v>
@@ -25057,7 +25057,7 @@
         <v>0</v>
       </c>
       <c r="O165">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="P165">
         <v>0</v>
@@ -25136,7 +25136,7 @@
         <v>0</v>
       </c>
       <c r="O166">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P166">
         <v>0</v>
@@ -25215,7 +25215,7 @@
         <v>0</v>
       </c>
       <c r="O167">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P167">
         <v>0</v>
@@ -25294,7 +25294,7 @@
         <v>0</v>
       </c>
       <c r="O168">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P168">
         <v>0</v>
@@ -25373,7 +25373,7 @@
         <v>0</v>
       </c>
       <c r="O169">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P169">
         <v>0</v>
@@ -25452,7 +25452,7 @@
         <v>0</v>
       </c>
       <c r="O170">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P170">
         <v>0</v>
@@ -25531,7 +25531,7 @@
         <v>0</v>
       </c>
       <c r="O171">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P171">
         <v>0</v>
@@ -25610,7 +25610,7 @@
         <v>0</v>
       </c>
       <c r="O172">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P172">
         <v>0</v>
@@ -25689,7 +25689,7 @@
         <v>0</v>
       </c>
       <c r="O173">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P173">
         <v>0</v>
@@ -25768,7 +25768,7 @@
         <v>0</v>
       </c>
       <c r="O174">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P174">
         <v>0</v>
@@ -25847,7 +25847,7 @@
         <v>0</v>
       </c>
       <c r="O175">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P175">
         <v>0</v>
@@ -25926,7 +25926,7 @@
         <v>0</v>
       </c>
       <c r="O176">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P176">
         <v>0</v>
@@ -26005,7 +26005,7 @@
         <v>0</v>
       </c>
       <c r="O177">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P177">
         <v>0</v>
@@ -26084,7 +26084,7 @@
         <v>0</v>
       </c>
       <c r="O178">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P178">
         <v>0</v>
@@ -26163,7 +26163,7 @@
         <v>0</v>
       </c>
       <c r="O179">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P179">
         <v>0</v>
@@ -26242,7 +26242,7 @@
         <v>0</v>
       </c>
       <c r="O180">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P180">
         <v>0</v>
@@ -26318,7 +26318,7 @@
         <v>0</v>
       </c>
       <c r="O181">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P181">
         <v>0</v>
@@ -26397,7 +26397,7 @@
         <v>0</v>
       </c>
       <c r="O182">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P182">
         <v>0</v>
@@ -26473,7 +26473,7 @@
         <v>0</v>
       </c>
       <c r="O183">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P183">
         <v>0</v>
@@ -26552,7 +26552,7 @@
         <v>0</v>
       </c>
       <c r="O184">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P184">
         <v>0</v>
@@ -26631,7 +26631,7 @@
         <v>0</v>
       </c>
       <c r="O185">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P185">
         <v>0</v>
@@ -26710,7 +26710,7 @@
         <v>0</v>
       </c>
       <c r="O186">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P186">
         <v>0</v>
@@ -26789,7 +26789,7 @@
         <v>0</v>
       </c>
       <c r="O187">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P187">
         <v>0</v>
@@ -26868,7 +26868,7 @@
         <v>0</v>
       </c>
       <c r="O188">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P188">
         <v>0</v>
@@ -26947,7 +26947,7 @@
         <v>0</v>
       </c>
       <c r="O189">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P189">
         <v>0</v>
@@ -27026,7 +27026,7 @@
         <v>0</v>
       </c>
       <c r="O190">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P190">
         <v>0</v>
@@ -27105,7 +27105,7 @@
         <v>0</v>
       </c>
       <c r="O191">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P191">
         <v>0</v>
@@ -27184,7 +27184,7 @@
         <v>0</v>
       </c>
       <c r="O192">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P192">
         <v>0</v>
@@ -27263,7 +27263,7 @@
         <v>0</v>
       </c>
       <c r="O193">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P193">
         <v>0</v>
@@ -27342,7 +27342,7 @@
         <v>0</v>
       </c>
       <c r="O194">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P194">
         <v>0</v>
@@ -27421,7 +27421,7 @@
         <v>0</v>
       </c>
       <c r="O195">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P195">
         <v>0</v>
@@ -27500,7 +27500,7 @@
         <v>0</v>
       </c>
       <c r="O196">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P196">
         <v>0</v>
@@ -27579,7 +27579,7 @@
         <v>0</v>
       </c>
       <c r="O197">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P197">
         <v>0</v>
@@ -27658,7 +27658,7 @@
         <v>0</v>
       </c>
       <c r="O198">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="P198">
         <v>0</v>
@@ -27737,7 +27737,7 @@
         <v>0</v>
       </c>
       <c r="O199">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P199">
         <v>0</v>
@@ -27816,7 +27816,7 @@
         <v>0</v>
       </c>
       <c r="O200">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P200">
         <v>0</v>
@@ -27895,7 +27895,7 @@
         <v>0</v>
       </c>
       <c r="O201">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P201">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="O202">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P202">
         <v>0</v>
@@ -28053,7 +28053,7 @@
         <v>0</v>
       </c>
       <c r="O203">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P203">
         <v>0</v>
@@ -28132,7 +28132,7 @@
         <v>0</v>
       </c>
       <c r="O204">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P204">
         <v>0</v>
@@ -28211,7 +28211,7 @@
         <v>0</v>
       </c>
       <c r="O205">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P205">
         <v>0</v>
@@ -28290,7 +28290,7 @@
         <v>0</v>
       </c>
       <c r="O206">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P206">
         <v>0</v>
@@ -28369,7 +28369,7 @@
         <v>0</v>
       </c>
       <c r="O207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P207">
         <v>0</v>
@@ -28448,7 +28448,7 @@
         <v>0</v>
       </c>
       <c r="O208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P208">
         <v>0</v>
@@ -28527,7 +28527,7 @@
         <v>0</v>
       </c>
       <c r="O209">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P209">
         <v>0</v>
@@ -28606,7 +28606,7 @@
         <v>0</v>
       </c>
       <c r="O210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P210">
         <v>0</v>
@@ -28685,7 +28685,7 @@
         <v>0</v>
       </c>
       <c r="O211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P211">
         <v>0</v>
@@ -28764,7 +28764,7 @@
         <v>0</v>
       </c>
       <c r="O212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P212">
         <v>0</v>
@@ -28843,7 +28843,7 @@
         <v>0</v>
       </c>
       <c r="O213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P213">
         <v>0</v>
@@ -29001,7 +29001,7 @@
         <v>0</v>
       </c>
       <c r="O215">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="P215">
         <v>0</v>
@@ -29080,7 +29080,7 @@
         <v>0</v>
       </c>
       <c r="O216">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="P216">
         <v>0</v>
@@ -29159,7 +29159,7 @@
         <v>0</v>
       </c>
       <c r="O217">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P217">
         <v>0</v>
@@ -29235,7 +29235,7 @@
         <v>0</v>
       </c>
       <c r="N218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O218">
         <v>0</v>
@@ -29475,7 +29475,7 @@
         <v>0</v>
       </c>
       <c r="O221">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P221">
         <v>0</v>
@@ -29554,7 +29554,7 @@
         <v>0</v>
       </c>
       <c r="O222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P222">
         <v>0</v>
@@ -29633,7 +29633,7 @@
         <v>0</v>
       </c>
       <c r="O223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P223">
         <v>0</v>
@@ -29712,7 +29712,7 @@
         <v>0</v>
       </c>
       <c r="O224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P224">
         <v>0</v>
@@ -29791,7 +29791,7 @@
         <v>0</v>
       </c>
       <c r="O225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P225">
         <v>0</v>
@@ -29870,7 +29870,7 @@
         <v>0</v>
       </c>
       <c r="O226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P226">
         <v>0</v>
@@ -29952,7 +29952,7 @@
         <v>0</v>
       </c>
       <c r="O227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P227">
         <v>0</v>
@@ -30034,7 +30034,7 @@
         <v>0</v>
       </c>
       <c r="O228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P228">
         <v>0</v>
@@ -30195,7 +30195,7 @@
         <v>0</v>
       </c>
       <c r="O230">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="P230">
         <v>0</v>
@@ -30277,7 +30277,7 @@
         <v>0</v>
       </c>
       <c r="O231">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="P231">
         <v>0</v>
@@ -30356,7 +30356,7 @@
         <v>0</v>
       </c>
       <c r="O232">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="P232">
         <v>0</v>
@@ -30435,7 +30435,7 @@
         <v>0</v>
       </c>
       <c r="O233">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P233">
         <v>0</v>
@@ -30514,7 +30514,7 @@
         <v>0</v>
       </c>
       <c r="O234">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P234">
         <v>0</v>
@@ -30593,7 +30593,7 @@
         <v>0</v>
       </c>
       <c r="O235">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P235">
         <v>0</v>
@@ -30672,7 +30672,7 @@
         <v>0</v>
       </c>
       <c r="O236">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P236">
         <v>0</v>
@@ -30751,7 +30751,7 @@
         <v>0</v>
       </c>
       <c r="O237">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P237">
         <v>0</v>
@@ -30830,7 +30830,7 @@
         <v>0</v>
       </c>
       <c r="O238">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P238">
         <v>0</v>
@@ -30909,7 +30909,7 @@
         <v>0</v>
       </c>
       <c r="O239">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P239">
         <v>0</v>
@@ -30988,7 +30988,7 @@
         <v>0</v>
       </c>
       <c r="O240">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P240">
         <v>0</v>
@@ -31067,7 +31067,7 @@
         <v>0</v>
       </c>
       <c r="O241">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P241">
         <v>0</v>
@@ -31146,7 +31146,7 @@
         <v>0</v>
       </c>
       <c r="O242">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P242">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>0</v>
       </c>
       <c r="O243">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="P243">
         <v>0</v>
@@ -31304,7 +31304,7 @@
         <v>0</v>
       </c>
       <c r="O244">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P244">
         <v>0</v>
@@ -31383,7 +31383,7 @@
         <v>0</v>
       </c>
       <c r="O245">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P245">
         <v>0</v>
@@ -31462,7 +31462,7 @@
         <v>0</v>
       </c>
       <c r="O246">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P246">
         <v>0</v>
@@ -31541,7 +31541,7 @@
         <v>0</v>
       </c>
       <c r="O247">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P247">
         <v>0</v>
@@ -31620,7 +31620,7 @@
         <v>0</v>
       </c>
       <c r="O248">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P248">
         <v>0</v>
@@ -31699,7 +31699,7 @@
         <v>0</v>
       </c>
       <c r="O249">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P249">
         <v>0</v>
@@ -31778,7 +31778,7 @@
         <v>0</v>
       </c>
       <c r="O250">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P250">
         <v>0</v>
@@ -31857,7 +31857,7 @@
         <v>0</v>
       </c>
       <c r="O251">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P251">
         <v>0</v>
@@ -31936,10 +31936,10 @@
         <v>0</v>
       </c>
       <c r="O252">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -32015,7 +32015,7 @@
         <v>0</v>
       </c>
       <c r="O253">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P253">
         <v>0</v>
@@ -32094,10 +32094,10 @@
         <v>0</v>
       </c>
       <c r="O254">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="P254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -32173,7 +32173,7 @@
         <v>0</v>
       </c>
       <c r="O255">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P255">
         <v>0</v>
@@ -32252,7 +32252,7 @@
         <v>0</v>
       </c>
       <c r="O256">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P256">
         <v>0</v>
@@ -32331,7 +32331,7 @@
         <v>0</v>
       </c>
       <c r="O257">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P257">
         <v>0</v>
@@ -32410,7 +32410,7 @@
         <v>0</v>
       </c>
       <c r="O258">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P258">
         <v>0</v>
@@ -32489,7 +32489,7 @@
         <v>0</v>
       </c>
       <c r="O259">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P259">
         <v>0</v>
@@ -32568,7 +32568,7 @@
         <v>0</v>
       </c>
       <c r="O260">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P260">
         <v>0</v>
@@ -32647,7 +32647,7 @@
         <v>0</v>
       </c>
       <c r="O261">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P261">
         <v>0</v>
@@ -32726,7 +32726,7 @@
         <v>0</v>
       </c>
       <c r="O262">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P262">
         <v>0</v>
@@ -32805,7 +32805,7 @@
         <v>0</v>
       </c>
       <c r="O263">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P263">
         <v>0</v>
@@ -32884,7 +32884,7 @@
         <v>0</v>
       </c>
       <c r="O264">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P264">
         <v>0</v>
@@ -32963,7 +32963,7 @@
         <v>0</v>
       </c>
       <c r="O265">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P265">
         <v>0</v>
@@ -33039,10 +33039,10 @@
         <v>0</v>
       </c>
       <c r="N266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P266">
         <v>0</v>
@@ -33121,7 +33121,7 @@
         <v>0</v>
       </c>
       <c r="O267">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P267">
         <v>0</v>
@@ -33200,7 +33200,7 @@
         <v>0</v>
       </c>
       <c r="O268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P268">
         <v>0</v>
@@ -33279,7 +33279,7 @@
         <v>0</v>
       </c>
       <c r="O269">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P269">
         <v>0</v>
@@ -33358,7 +33358,7 @@
         <v>0</v>
       </c>
       <c r="O270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P270">
         <v>0</v>
@@ -33516,7 +33516,7 @@
         <v>0</v>
       </c>
       <c r="O272">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="P272">
         <v>0</v>
@@ -33595,7 +33595,7 @@
         <v>0</v>
       </c>
       <c r="O273">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="P273">
         <v>0</v>
@@ -33674,7 +33674,7 @@
         <v>0</v>
       </c>
       <c r="O274">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="P274">
         <v>0</v>
@@ -33753,7 +33753,7 @@
         <v>0</v>
       </c>
       <c r="O275">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="P275">
         <v>0</v>
@@ -33832,7 +33832,7 @@
         <v>0</v>
       </c>
       <c r="O276">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="P276">
         <v>0</v>
@@ -33911,7 +33911,7 @@
         <v>0</v>
       </c>
       <c r="O277">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="P277">
         <v>0</v>
@@ -33990,7 +33990,7 @@
         <v>0</v>
       </c>
       <c r="O278">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="P278">
         <v>0</v>
@@ -34069,7 +34069,7 @@
         <v>0</v>
       </c>
       <c r="O279">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="P279">
         <v>0</v>
@@ -34148,7 +34148,7 @@
         <v>0</v>
       </c>
       <c r="O280">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="P280">
         <v>0</v>
@@ -34227,7 +34227,7 @@
         <v>0</v>
       </c>
       <c r="O281">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="P281">
         <v>0</v>
@@ -34306,7 +34306,7 @@
         <v>0</v>
       </c>
       <c r="O282">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="P282">
         <v>0</v>
@@ -34385,7 +34385,7 @@
         <v>0</v>
       </c>
       <c r="O283">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="P283">
         <v>0</v>
@@ -34464,7 +34464,7 @@
         <v>0</v>
       </c>
       <c r="O284">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="P284">
         <v>0</v>
@@ -34543,7 +34543,7 @@
         <v>0</v>
       </c>
       <c r="O285">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P285">
         <v>0</v>
@@ -34622,7 +34622,7 @@
         <v>0</v>
       </c>
       <c r="O286">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="P286">
         <v>0</v>
@@ -34701,7 +34701,7 @@
         <v>0</v>
       </c>
       <c r="O287">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="P287">
         <v>0</v>
@@ -34780,7 +34780,7 @@
         <v>0</v>
       </c>
       <c r="O288">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="P288">
         <v>0</v>
@@ -34859,7 +34859,7 @@
         <v>0</v>
       </c>
       <c r="O289">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P289">
         <v>0</v>
@@ -34938,7 +34938,7 @@
         <v>0</v>
       </c>
       <c r="O290">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="P290">
         <v>0</v>
@@ -35017,7 +35017,7 @@
         <v>0</v>
       </c>
       <c r="O291">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P291">
         <v>0</v>
@@ -35093,10 +35093,10 @@
         <v>0</v>
       </c>
       <c r="N292">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O292">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="P292">
         <v>0</v>
@@ -35175,7 +35175,7 @@
         <v>0</v>
       </c>
       <c r="O293">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="P293">
         <v>0</v>
@@ -35251,10 +35251,10 @@
         <v>0</v>
       </c>
       <c r="N294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O294">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P294">
         <v>0</v>
@@ -35333,7 +35333,7 @@
         <v>0</v>
       </c>
       <c r="O295">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="P295">
         <v>0</v>
@@ -35412,7 +35412,7 @@
         <v>0</v>
       </c>
       <c r="O296">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P296">
         <v>0</v>
@@ -35491,7 +35491,7 @@
         <v>0</v>
       </c>
       <c r="O297">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P297">
         <v>0</v>
@@ -35567,7 +35567,7 @@
         <v>0</v>
       </c>
       <c r="O298">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P298">
         <v>0</v>
@@ -35646,7 +35646,7 @@
         <v>0</v>
       </c>
       <c r="O299">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P299">
         <v>0</v>
@@ -35725,7 +35725,7 @@
         <v>0</v>
       </c>
       <c r="O300">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="P300">
         <v>0</v>
@@ -35804,7 +35804,7 @@
         <v>0</v>
       </c>
       <c r="O301">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="P301">
         <v>0</v>
@@ -35880,7 +35880,7 @@
         <v>0</v>
       </c>
       <c r="O302">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P302">
         <v>0</v>
@@ -35959,7 +35959,7 @@
         <v>0</v>
       </c>
       <c r="O303">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P303">
         <v>0</v>
@@ -36035,10 +36035,10 @@
         <v>0</v>
       </c>
       <c r="N304">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O304">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="P304">
         <v>0</v>
@@ -36117,7 +36117,7 @@
         <v>0</v>
       </c>
       <c r="O305">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P305">
         <v>0</v>
@@ -36196,7 +36196,7 @@
         <v>0</v>
       </c>
       <c r="O306">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P306">
         <v>0</v>
@@ -36275,7 +36275,7 @@
         <v>0</v>
       </c>
       <c r="O307">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="P307">
         <v>0</v>
@@ -36354,7 +36354,7 @@
         <v>0</v>
       </c>
       <c r="O308">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="P308">
         <v>0</v>
@@ -36433,7 +36433,7 @@
         <v>0</v>
       </c>
       <c r="O309">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P309">
         <v>0</v>
@@ -36512,7 +36512,7 @@
         <v>0</v>
       </c>
       <c r="O310">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P310">
         <v>0</v>
@@ -36591,7 +36591,7 @@
         <v>0</v>
       </c>
       <c r="O311">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="P311">
         <v>0</v>
@@ -36670,7 +36670,7 @@
         <v>0</v>
       </c>
       <c r="O312">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P312">
         <v>0</v>
@@ -36749,7 +36749,7 @@
         <v>0</v>
       </c>
       <c r="O313">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P313">
         <v>0</v>
@@ -36828,7 +36828,7 @@
         <v>0</v>
       </c>
       <c r="O314">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P314">
         <v>0</v>
@@ -36907,7 +36907,7 @@
         <v>0</v>
       </c>
       <c r="O315">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P315">
         <v>0</v>
@@ -36986,7 +36986,7 @@
         <v>0</v>
       </c>
       <c r="O316">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P316">
         <v>0</v>
@@ -37065,7 +37065,7 @@
         <v>0</v>
       </c>
       <c r="O317">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P317">
         <v>0</v>
@@ -37144,7 +37144,7 @@
         <v>0</v>
       </c>
       <c r="O318">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="P318">
         <v>0</v>
@@ -37223,7 +37223,7 @@
         <v>0</v>
       </c>
       <c r="O319">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="P319">
         <v>0</v>
@@ -37302,7 +37302,7 @@
         <v>0</v>
       </c>
       <c r="O320">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P320">
         <v>0</v>
@@ -37381,7 +37381,7 @@
         <v>0</v>
       </c>
       <c r="O321">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P321">
         <v>0</v>
@@ -37460,7 +37460,7 @@
         <v>0</v>
       </c>
       <c r="O322">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="P322">
         <v>0</v>
@@ -37539,7 +37539,7 @@
         <v>0</v>
       </c>
       <c r="O323">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P323">
         <v>0</v>
@@ -37618,7 +37618,7 @@
         <v>0</v>
       </c>
       <c r="O324">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P324">
         <v>0</v>
@@ -37697,7 +37697,7 @@
         <v>0</v>
       </c>
       <c r="O325">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P325">
         <v>0</v>
@@ -37776,7 +37776,7 @@
         <v>0</v>
       </c>
       <c r="O326">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P326">
         <v>0</v>
@@ -37855,7 +37855,7 @@
         <v>0</v>
       </c>
       <c r="O327">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P327">
         <v>0</v>
@@ -37934,7 +37934,7 @@
         <v>0</v>
       </c>
       <c r="O328">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P328">
         <v>0</v>
@@ -38013,7 +38013,7 @@
         <v>0</v>
       </c>
       <c r="O329">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P329">
         <v>0</v>
@@ -38092,7 +38092,7 @@
         <v>0</v>
       </c>
       <c r="O330">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P330">
         <v>0</v>
@@ -38171,7 +38171,7 @@
         <v>0</v>
       </c>
       <c r="O331">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P331">
         <v>0</v>
@@ -38250,7 +38250,7 @@
         <v>0</v>
       </c>
       <c r="O332">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P332">
         <v>0</v>
@@ -38329,7 +38329,7 @@
         <v>0</v>
       </c>
       <c r="O333">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P333">
         <v>0</v>
@@ -38408,7 +38408,7 @@
         <v>0</v>
       </c>
       <c r="O334">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P334">
         <v>0</v>
@@ -38487,7 +38487,7 @@
         <v>0</v>
       </c>
       <c r="O335">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P335">
         <v>0</v>
@@ -38566,7 +38566,7 @@
         <v>0</v>
       </c>
       <c r="O336">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P336">
         <v>0</v>
@@ -38645,7 +38645,7 @@
         <v>0</v>
       </c>
       <c r="O337">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P337">
         <v>0</v>
@@ -38724,7 +38724,7 @@
         <v>0</v>
       </c>
       <c r="O338">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P338">
         <v>0</v>
@@ -38803,7 +38803,7 @@
         <v>0</v>
       </c>
       <c r="O339">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P339">
         <v>0</v>
@@ -38882,7 +38882,7 @@
         <v>0</v>
       </c>
       <c r="O340">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P340">
         <v>0</v>
@@ -38961,7 +38961,7 @@
         <v>0</v>
       </c>
       <c r="O341">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P341">
         <v>0</v>
@@ -39040,7 +39040,7 @@
         <v>0</v>
       </c>
       <c r="O342">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P342">
         <v>0</v>
@@ -39119,7 +39119,7 @@
         <v>0</v>
       </c>
       <c r="O343">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P343">
         <v>0</v>
@@ -39198,7 +39198,7 @@
         <v>0</v>
       </c>
       <c r="O344">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="P344">
         <v>0</v>
@@ -39277,7 +39277,7 @@
         <v>0</v>
       </c>
       <c r="O345">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P345">
         <v>0</v>
@@ -39356,7 +39356,7 @@
         <v>0</v>
       </c>
       <c r="O346">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P346">
         <v>0</v>
@@ -39435,7 +39435,7 @@
         <v>0</v>
       </c>
       <c r="O347">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P347">
         <v>0</v>
@@ -39514,7 +39514,7 @@
         <v>0</v>
       </c>
       <c r="O348">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P348">
         <v>0</v>
@@ -39593,7 +39593,7 @@
         <v>0</v>
       </c>
       <c r="O349">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P349">
         <v>0</v>
@@ -39672,7 +39672,7 @@
         <v>0</v>
       </c>
       <c r="O350">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P350">
         <v>0</v>
@@ -39751,7 +39751,7 @@
         <v>0</v>
       </c>
       <c r="O351">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P351">
         <v>0</v>
@@ -39830,7 +39830,7 @@
         <v>0</v>
       </c>
       <c r="O352">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P352">
         <v>0</v>
@@ -39909,7 +39909,7 @@
         <v>0</v>
       </c>
       <c r="O353">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P353">
         <v>0</v>
@@ -39988,7 +39988,7 @@
         <v>0</v>
       </c>
       <c r="O354">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P354">
         <v>0</v>
@@ -40067,7 +40067,7 @@
         <v>0</v>
       </c>
       <c r="O355">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="P355">
         <v>0</v>
@@ -40146,7 +40146,7 @@
         <v>0</v>
       </c>
       <c r="O356">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P356">
         <v>0</v>
@@ -40225,7 +40225,7 @@
         <v>0</v>
       </c>
       <c r="O357">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P357">
         <v>0</v>
@@ -40304,7 +40304,7 @@
         <v>0</v>
       </c>
       <c r="O358">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P358">
         <v>0</v>
@@ -40383,7 +40383,7 @@
         <v>0</v>
       </c>
       <c r="O359">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P359">
         <v>0</v>
@@ -40462,7 +40462,7 @@
         <v>0</v>
       </c>
       <c r="O360">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P360">
         <v>0</v>
@@ -40541,7 +40541,7 @@
         <v>0</v>
       </c>
       <c r="O361">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P361">
         <v>0</v>
@@ -40620,7 +40620,7 @@
         <v>0</v>
       </c>
       <c r="O362">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P362">
         <v>0</v>
@@ -40699,7 +40699,7 @@
         <v>0</v>
       </c>
       <c r="O363">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P363">
         <v>0</v>
@@ -40778,7 +40778,7 @@
         <v>0</v>
       </c>
       <c r="O364">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P364">
         <v>0</v>
@@ -40857,7 +40857,7 @@
         <v>0</v>
       </c>
       <c r="O365">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P365">
         <v>0</v>
@@ -40936,7 +40936,7 @@
         <v>0</v>
       </c>
       <c r="O366">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P366">
         <v>0</v>
@@ -41015,7 +41015,7 @@
         <v>0</v>
       </c>
       <c r="O367">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P367">
         <v>0</v>
@@ -41413,7 +41413,7 @@
         <v>0</v>
       </c>
       <c r="N372">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O372">
         <v>0</v>
@@ -41574,7 +41574,7 @@
         <v>0</v>
       </c>
       <c r="N374">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O374">
         <v>0</v>
@@ -41653,7 +41653,7 @@
         <v>0</v>
       </c>
       <c r="N375">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O375">
         <v>0</v>
@@ -41732,7 +41732,7 @@
         <v>0</v>
       </c>
       <c r="N376">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O376">
         <v>0</v>
@@ -41811,7 +41811,7 @@
         <v>0</v>
       </c>
       <c r="N377">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O377">
         <v>0</v>
@@ -41975,7 +41975,7 @@
         <v>0</v>
       </c>
       <c r="O379">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P379">
         <v>0</v>
@@ -42051,7 +42051,7 @@
         <v>0</v>
       </c>
       <c r="O380">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P380">
         <v>0</v>
@@ -42130,7 +42130,7 @@
         <v>0</v>
       </c>
       <c r="O381">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P381">
         <v>0</v>
@@ -42209,7 +42209,7 @@
         <v>0</v>
       </c>
       <c r="O382">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P382">
         <v>0</v>
@@ -42367,7 +42367,7 @@
         <v>0</v>
       </c>
       <c r="O384">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P384">
         <v>0</v>
@@ -42443,10 +42443,10 @@
         <v>0</v>
       </c>
       <c r="N385">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O385">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P385">
         <v>0</v>
@@ -42528,7 +42528,7 @@
         <v>0</v>
       </c>
       <c r="O386">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P386">
         <v>0</v>
@@ -42601,10 +42601,10 @@
         <v>0</v>
       </c>
       <c r="N387">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O387">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P387">
         <v>0</v>
@@ -42680,10 +42680,10 @@
         <v>0</v>
       </c>
       <c r="N388">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O388">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P388">
         <v>0</v>
@@ -42762,7 +42762,7 @@
         <v>0</v>
       </c>
       <c r="O389">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P389">
         <v>0</v>
@@ -42841,7 +42841,7 @@
         <v>0</v>
       </c>
       <c r="O390">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P390">
         <v>0</v>
@@ -42917,10 +42917,10 @@
         <v>0</v>
       </c>
       <c r="N391">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O391">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P391">
         <v>0</v>
@@ -43002,7 +43002,7 @@
         <v>0</v>
       </c>
       <c r="O392">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P392">
         <v>0</v>
@@ -43081,7 +43081,7 @@
         <v>0</v>
       </c>
       <c r="O393">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P393">
         <v>0</v>
@@ -43160,7 +43160,7 @@
         <v>0</v>
       </c>
       <c r="O394">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P394">
         <v>0</v>
@@ -43239,7 +43239,7 @@
         <v>0</v>
       </c>
       <c r="O395">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P395">
         <v>0</v>
@@ -43394,7 +43394,7 @@
         <v>0</v>
       </c>
       <c r="N397">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O397">
         <v>0</v>
@@ -43476,7 +43476,7 @@
         <v>0</v>
       </c>
       <c r="N398">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O398">
         <v>0</v>
@@ -43556,7 +43556,7 @@
         <v>0</v>
       </c>
       <c r="N399">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O399">
         <v>0</v>
@@ -43717,7 +43717,7 @@
         <v>0</v>
       </c>
       <c r="N401">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O401">
         <v>0</v>
@@ -43875,7 +43875,7 @@
         <v>0</v>
       </c>
       <c r="N403">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="O403">
         <v>0</v>
@@ -43954,7 +43954,7 @@
         <v>0</v>
       </c>
       <c r="N404">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="O404">
         <v>0</v>
@@ -44033,10 +44033,10 @@
         <v>0</v>
       </c>
       <c r="N405">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="O405">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P405">
         <v>0</v>
@@ -44112,7 +44112,7 @@
         <v>0</v>
       </c>
       <c r="N406">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="O406">
         <v>0</v>
@@ -44191,10 +44191,10 @@
         <v>0</v>
       </c>
       <c r="N407">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="O407">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P407">
         <v>0</v>
@@ -44270,7 +44270,7 @@
         <v>0</v>
       </c>
       <c r="N408">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="O408">
         <v>0</v>
@@ -44349,7 +44349,7 @@
         <v>0</v>
       </c>
       <c r="N409">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="O409">
         <v>0</v>
@@ -44425,7 +44425,7 @@
         <v>0</v>
       </c>
       <c r="N410">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="O410">
         <v>0</v>
@@ -44504,7 +44504,7 @@
         <v>0</v>
       </c>
       <c r="N411">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="O411">
         <v>0</v>
@@ -44583,7 +44583,7 @@
         <v>0</v>
       </c>
       <c r="N412">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O412">
         <v>0</v>
@@ -44662,7 +44662,7 @@
         <v>0</v>
       </c>
       <c r="N413">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O413">
         <v>0</v>
@@ -44741,7 +44741,7 @@
         <v>0</v>
       </c>
       <c r="N414">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O414">
         <v>0</v>
@@ -44820,7 +44820,7 @@
         <v>0</v>
       </c>
       <c r="N415">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="O415">
         <v>0</v>
@@ -44899,7 +44899,7 @@
         <v>0</v>
       </c>
       <c r="N416">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O416">
         <v>0</v>
@@ -44978,7 +44978,7 @@
         <v>0</v>
       </c>
       <c r="N417">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O417">
         <v>0</v>
@@ -45057,7 +45057,7 @@
         <v>0</v>
       </c>
       <c r="N418">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O418">
         <v>0</v>
@@ -45136,7 +45136,7 @@
         <v>0</v>
       </c>
       <c r="N419">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O419">
         <v>0</v>
@@ -45215,7 +45215,7 @@
         <v>0</v>
       </c>
       <c r="N420">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="O420">
         <v>0</v>
@@ -45294,7 +45294,7 @@
         <v>0</v>
       </c>
       <c r="N421">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O421">
         <v>0</v>
@@ -45373,10 +45373,10 @@
         <v>0</v>
       </c>
       <c r="N422">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O422">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P422">
         <v>0</v>
@@ -45452,7 +45452,7 @@
         <v>0</v>
       </c>
       <c r="N423">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O423">
         <v>0</v>
@@ -45528,7 +45528,7 @@
         <v>0</v>
       </c>
       <c r="N424">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O424">
         <v>0</v>
@@ -45607,7 +45607,7 @@
         <v>0</v>
       </c>
       <c r="N425">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O425">
         <v>0</v>
@@ -45686,7 +45686,7 @@
         <v>0</v>
       </c>
       <c r="N426">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O426">
         <v>0</v>
@@ -45765,13 +45765,13 @@
         <v>1</v>
       </c>
       <c r="N427">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O427">
         <v>0</v>
       </c>
       <c r="P427">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q427">
         <v>0</v>
@@ -45844,10 +45844,10 @@
         <v>0</v>
       </c>
       <c r="N428">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O428">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P428">
         <v>0</v>
@@ -45923,7 +45923,7 @@
         <v>0</v>
       </c>
       <c r="N429">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O429">
         <v>0</v>
@@ -46002,7 +46002,7 @@
         <v>0</v>
       </c>
       <c r="N430">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O430">
         <v>0</v>
@@ -46081,7 +46081,7 @@
         <v>0</v>
       </c>
       <c r="N431">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O431">
         <v>0</v>
@@ -46160,7 +46160,7 @@
         <v>0</v>
       </c>
       <c r="N432">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="O432">
         <v>0</v>
@@ -46239,7 +46239,7 @@
         <v>0</v>
       </c>
       <c r="N433">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="O433">
         <v>0</v>
@@ -46318,10 +46318,10 @@
         <v>0</v>
       </c>
       <c r="N434">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O434">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P434">
         <v>0</v>
@@ -46397,10 +46397,10 @@
         <v>0</v>
       </c>
       <c r="N435">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="O435">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P435">
         <v>0</v>
@@ -46476,10 +46476,10 @@
         <v>0</v>
       </c>
       <c r="N436">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O436">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P436">
         <v>0</v>
@@ -46558,7 +46558,7 @@
         <v>0</v>
       </c>
       <c r="O437">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="P437">
         <v>0</v>
@@ -46637,7 +46637,7 @@
         <v>0</v>
       </c>
       <c r="O438">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P438">
         <v>0</v>
@@ -46713,7 +46713,7 @@
         <v>0</v>
       </c>
       <c r="N439">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O439">
         <v>0</v>
@@ -46795,7 +46795,7 @@
         <v>0</v>
       </c>
       <c r="O440">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P440">
         <v>0</v>
@@ -46874,7 +46874,7 @@
         <v>0</v>
       </c>
       <c r="O441">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P441">
         <v>0</v>
@@ -46953,7 +46953,7 @@
         <v>0</v>
       </c>
       <c r="O442">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P442">
         <v>0</v>
@@ -47029,10 +47029,10 @@
         <v>0</v>
       </c>
       <c r="N443">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O443">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P443">
         <v>0</v>
@@ -47111,7 +47111,7 @@
         <v>0</v>
       </c>
       <c r="O444">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P444">
         <v>0</v>
@@ -47190,7 +47190,7 @@
         <v>0</v>
       </c>
       <c r="O445">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P445">
         <v>0</v>
@@ -47269,7 +47269,7 @@
         <v>0</v>
       </c>
       <c r="O446">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P446">
         <v>0</v>
@@ -47348,7 +47348,7 @@
         <v>0</v>
       </c>
       <c r="O447">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P447">
         <v>0</v>
@@ -47427,7 +47427,7 @@
         <v>0</v>
       </c>
       <c r="O448">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P448">
         <v>0</v>
@@ -47506,7 +47506,7 @@
         <v>0</v>
       </c>
       <c r="O449">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P449">
         <v>0</v>
@@ -47582,7 +47582,7 @@
         <v>0</v>
       </c>
       <c r="N450">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O450">
         <v>0</v>
@@ -47664,7 +47664,7 @@
         <v>0</v>
       </c>
       <c r="O451">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P451">
         <v>0</v>
@@ -47743,7 +47743,7 @@
         <v>0</v>
       </c>
       <c r="O452">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P452">
         <v>0</v>
@@ -47822,7 +47822,7 @@
         <v>0</v>
       </c>
       <c r="O453">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P453">
         <v>0</v>
@@ -47898,7 +47898,7 @@
         <v>0</v>
       </c>
       <c r="N454">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O454">
         <v>0</v>
@@ -47980,7 +47980,7 @@
         <v>0</v>
       </c>
       <c r="O455">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P455">
         <v>0</v>
@@ -48059,10 +48059,10 @@
         <v>0</v>
       </c>
       <c r="O456">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P456">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q456">
         <v>0</v>
@@ -48138,7 +48138,7 @@
         <v>0</v>
       </c>
       <c r="O457">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P457">
         <v>0</v>
@@ -48217,7 +48217,7 @@
         <v>0</v>
       </c>
       <c r="O458">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P458">
         <v>0</v>
@@ -48296,7 +48296,7 @@
         <v>0</v>
       </c>
       <c r="O459">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P459">
         <v>0</v>
@@ -48375,7 +48375,7 @@
         <v>0</v>
       </c>
       <c r="O460">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P460">
         <v>0</v>
@@ -48451,7 +48451,7 @@
         <v>0</v>
       </c>
       <c r="N461">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O461">
         <v>0</v>
@@ -48533,7 +48533,7 @@
         <v>0</v>
       </c>
       <c r="O462">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P462">
         <v>0</v>
@@ -48609,10 +48609,10 @@
         <v>0</v>
       </c>
       <c r="N463">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O463">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P463">
         <v>0</v>
@@ -48688,7 +48688,7 @@
         <v>0</v>
       </c>
       <c r="N464">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O464">
         <v>0</v>
@@ -48770,7 +48770,7 @@
         <v>0</v>
       </c>
       <c r="O465">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P465">
         <v>0</v>
@@ -48849,7 +48849,7 @@
         <v>0</v>
       </c>
       <c r="O466">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P466">
         <v>0</v>
@@ -48925,7 +48925,7 @@
         <v>0</v>
       </c>
       <c r="N467">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O467">
         <v>0</v>
@@ -49004,7 +49004,7 @@
         <v>0</v>
       </c>
       <c r="N468">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O468">
         <v>0</v>
@@ -49083,7 +49083,7 @@
         <v>0</v>
       </c>
       <c r="N469">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O469">
         <v>0</v>
@@ -49162,7 +49162,7 @@
         <v>0</v>
       </c>
       <c r="N470">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O470">
         <v>0</v>
@@ -49244,7 +49244,7 @@
         <v>0</v>
       </c>
       <c r="O471">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P471">
         <v>0</v>
@@ -49323,7 +49323,7 @@
         <v>0</v>
       </c>
       <c r="O472">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P472">
         <v>0</v>
@@ -49402,7 +49402,7 @@
         <v>0</v>
       </c>
       <c r="O473">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P473">
         <v>0</v>
@@ -49481,7 +49481,7 @@
         <v>0</v>
       </c>
       <c r="O474">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P474">
         <v>0</v>
@@ -49557,7 +49557,7 @@
         <v>0</v>
       </c>
       <c r="N475">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O475">
         <v>0</v>
@@ -49639,7 +49639,7 @@
         <v>0</v>
       </c>
       <c r="O476">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P476">
         <v>0</v>
@@ -49718,7 +49718,7 @@
         <v>0</v>
       </c>
       <c r="O477">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P477">
         <v>0</v>
@@ -49794,7 +49794,7 @@
         <v>0</v>
       </c>
       <c r="N478">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O478">
         <v>0</v>
@@ -49876,7 +49876,7 @@
         <v>0</v>
       </c>
       <c r="O479">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P479">
         <v>0</v>
@@ -49952,7 +49952,7 @@
         <v>0</v>
       </c>
       <c r="N480">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O480">
         <v>0</v>
@@ -50034,7 +50034,7 @@
         <v>0</v>
       </c>
       <c r="O481">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P481">
         <v>0</v>
@@ -50110,10 +50110,10 @@
         <v>0</v>
       </c>
       <c r="N482">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O482">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P482">
         <v>0</v>
@@ -50192,7 +50192,7 @@
         <v>0</v>
       </c>
       <c r="O483">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P483">
         <v>0</v>
@@ -50271,7 +50271,7 @@
         <v>0</v>
       </c>
       <c r="O484">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P484">
         <v>0</v>
@@ -50350,7 +50350,7 @@
         <v>0</v>
       </c>
       <c r="O485">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P485">
         <v>0</v>
@@ -50429,7 +50429,7 @@
         <v>0</v>
       </c>
       <c r="O486">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P486">
         <v>0</v>
@@ -50508,7 +50508,7 @@
         <v>0</v>
       </c>
       <c r="O487">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P487">
         <v>0</v>
@@ -50584,7 +50584,7 @@
         <v>0</v>
       </c>
       <c r="N488">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O488">
         <v>0</v>
@@ -50742,10 +50742,10 @@
         <v>0</v>
       </c>
       <c r="N490">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O490">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P490">
         <v>0</v>
@@ -50824,7 +50824,7 @@
         <v>0</v>
       </c>
       <c r="O491">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P491">
         <v>0</v>
@@ -50903,7 +50903,7 @@
         <v>0</v>
       </c>
       <c r="O492">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P492">
         <v>0</v>
@@ -50982,7 +50982,7 @@
         <v>0</v>
       </c>
       <c r="O493">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P493">
         <v>0</v>
@@ -51137,10 +51137,10 @@
         <v>0</v>
       </c>
       <c r="N495">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O495">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P495">
         <v>0</v>
@@ -51219,7 +51219,7 @@
         <v>0</v>
       </c>
       <c r="O496">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P496">
         <v>0</v>
@@ -51295,7 +51295,7 @@
         <v>0</v>
       </c>
       <c r="N497">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O497">
         <v>0</v>
@@ -51377,7 +51377,7 @@
         <v>0</v>
       </c>
       <c r="O498">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P498">
         <v>0</v>
@@ -51456,7 +51456,7 @@
         <v>0</v>
       </c>
       <c r="O499">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P499">
         <v>0</v>
@@ -51532,7 +51532,7 @@
         <v>0</v>
       </c>
       <c r="N500">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O500">
         <v>0</v>
@@ -51772,7 +51772,7 @@
         <v>0</v>
       </c>
       <c r="O503">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P503">
         <v>0</v>
@@ -51851,7 +51851,7 @@
         <v>0</v>
       </c>
       <c r="O504">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P504">
         <v>0</v>
@@ -51930,7 +51930,7 @@
         <v>0</v>
       </c>
       <c r="O505">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P505">
         <v>0</v>
@@ -52009,7 +52009,7 @@
         <v>0</v>
       </c>
       <c r="O506">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P506">
         <v>0</v>
@@ -52088,7 +52088,7 @@
         <v>0</v>
       </c>
       <c r="O507">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P507">
         <v>0</v>
@@ -52167,7 +52167,7 @@
         <v>0</v>
       </c>
       <c r="O508">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P508">
         <v>0</v>
@@ -52246,7 +52246,7 @@
         <v>0</v>
       </c>
       <c r="O509">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P509">
         <v>0</v>
@@ -52325,7 +52325,7 @@
         <v>0</v>
       </c>
       <c r="O510">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P510">
         <v>0</v>
@@ -52404,7 +52404,7 @@
         <v>0</v>
       </c>
       <c r="O511">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P511">
         <v>0</v>
@@ -52483,7 +52483,7 @@
         <v>0</v>
       </c>
       <c r="O512">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P512">
         <v>0</v>
@@ -52562,7 +52562,7 @@
         <v>0</v>
       </c>
       <c r="O513">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P513">
         <v>0</v>
@@ -52641,7 +52641,7 @@
         <v>0</v>
       </c>
       <c r="O514">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P514">
         <v>0</v>
@@ -52720,7 +52720,7 @@
         <v>0</v>
       </c>
       <c r="O515">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P515">
         <v>0</v>
@@ -52799,7 +52799,7 @@
         <v>0</v>
       </c>
       <c r="O516">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P516">
         <v>0</v>
@@ -52878,7 +52878,7 @@
         <v>0</v>
       </c>
       <c r="O517">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P517">
         <v>0</v>
@@ -52957,7 +52957,7 @@
         <v>0</v>
       </c>
       <c r="O518">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P518">
         <v>0</v>
@@ -53036,7 +53036,7 @@
         <v>0</v>
       </c>
       <c r="O519">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P519">
         <v>0</v>
@@ -53115,7 +53115,7 @@
         <v>0</v>
       </c>
       <c r="O520">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P520">
         <v>0</v>
@@ -53194,7 +53194,7 @@
         <v>0</v>
       </c>
       <c r="O521">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P521">
         <v>0</v>
@@ -53273,7 +53273,7 @@
         <v>0</v>
       </c>
       <c r="O522">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P522">
         <v>0</v>
@@ -53352,7 +53352,7 @@
         <v>0</v>
       </c>
       <c r="O523">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P523">
         <v>0</v>
@@ -53431,7 +53431,7 @@
         <v>0</v>
       </c>
       <c r="O524">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P524">
         <v>0</v>
@@ -53510,7 +53510,7 @@
         <v>0</v>
       </c>
       <c r="O525">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P525">
         <v>0</v>
@@ -53589,7 +53589,7 @@
         <v>0</v>
       </c>
       <c r="O526">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P526">
         <v>0</v>
@@ -53668,7 +53668,7 @@
         <v>0</v>
       </c>
       <c r="O527">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P527">
         <v>0</v>
@@ -53747,7 +53747,7 @@
         <v>0</v>
       </c>
       <c r="O528">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P528">
         <v>0</v>
@@ -53826,7 +53826,7 @@
         <v>0</v>
       </c>
       <c r="O529">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P529">
         <v>0</v>
@@ -53905,7 +53905,7 @@
         <v>0</v>
       </c>
       <c r="O530">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P530">
         <v>0</v>
@@ -53984,7 +53984,7 @@
         <v>0</v>
       </c>
       <c r="O531">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P531">
         <v>0</v>
@@ -54063,7 +54063,7 @@
         <v>0</v>
       </c>
       <c r="O532">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P532">
         <v>0</v>
@@ -54142,7 +54142,7 @@
         <v>0</v>
       </c>
       <c r="O533">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P533">
         <v>0</v>
@@ -54221,7 +54221,7 @@
         <v>0</v>
       </c>
       <c r="O534">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P534">
         <v>0</v>
@@ -54300,7 +54300,7 @@
         <v>0</v>
       </c>
       <c r="O535">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P535">
         <v>0</v>
@@ -54379,7 +54379,7 @@
         <v>0</v>
       </c>
       <c r="O536">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P536">
         <v>0</v>
@@ -54458,7 +54458,7 @@
         <v>0</v>
       </c>
       <c r="O537">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P537">
         <v>0</v>
@@ -54537,7 +54537,7 @@
         <v>0</v>
       </c>
       <c r="O538">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P538">
         <v>0</v>
@@ -54616,7 +54616,7 @@
         <v>0</v>
       </c>
       <c r="O539">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P539">
         <v>0</v>
@@ -54695,7 +54695,7 @@
         <v>0</v>
       </c>
       <c r="O540">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P540">
         <v>0</v>
@@ -54774,7 +54774,7 @@
         <v>0</v>
       </c>
       <c r="O541">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P541">
         <v>0</v>
@@ -54853,7 +54853,7 @@
         <v>0</v>
       </c>
       <c r="O542">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P542">
         <v>0</v>
@@ -54932,7 +54932,7 @@
         <v>0</v>
       </c>
       <c r="O543">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P543">
         <v>0</v>
@@ -55011,7 +55011,7 @@
         <v>0</v>
       </c>
       <c r="O544">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P544">
         <v>0</v>
@@ -55169,7 +55169,7 @@
         <v>0</v>
       </c>
       <c r="O546">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P546">
         <v>0</v>
@@ -55248,7 +55248,7 @@
         <v>0</v>
       </c>
       <c r="O547">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P547">
         <v>0</v>
@@ -55324,7 +55324,7 @@
         <v>0</v>
       </c>
       <c r="O548">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P548">
         <v>0</v>
@@ -55403,7 +55403,7 @@
         <v>0</v>
       </c>
       <c r="O549">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P549">
         <v>0</v>
@@ -55482,7 +55482,7 @@
         <v>0</v>
       </c>
       <c r="O550">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P550">
         <v>0</v>
@@ -55561,7 +55561,7 @@
         <v>0</v>
       </c>
       <c r="O551">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P551">
         <v>0</v>
@@ -55640,7 +55640,7 @@
         <v>0</v>
       </c>
       <c r="O552">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P552">
         <v>0</v>
@@ -55719,7 +55719,7 @@
         <v>0</v>
       </c>
       <c r="O553">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P553">
         <v>0</v>
@@ -55798,7 +55798,7 @@
         <v>0</v>
       </c>
       <c r="O554">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P554">
         <v>0</v>
@@ -55877,7 +55877,7 @@
         <v>0</v>
       </c>
       <c r="O555">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P555">
         <v>0</v>
@@ -55956,7 +55956,7 @@
         <v>0</v>
       </c>
       <c r="O556">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P556">
         <v>0</v>
@@ -56035,7 +56035,7 @@
         <v>0</v>
       </c>
       <c r="O557">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P557">
         <v>0</v>
@@ -56114,7 +56114,7 @@
         <v>0</v>
       </c>
       <c r="O558">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P558">
         <v>0</v>
@@ -56193,7 +56193,7 @@
         <v>0</v>
       </c>
       <c r="O559">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P559">
         <v>0</v>
@@ -56272,7 +56272,7 @@
         <v>0</v>
       </c>
       <c r="O560">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P560">
         <v>0</v>
@@ -56351,7 +56351,7 @@
         <v>0</v>
       </c>
       <c r="O561">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P561">
         <v>0</v>
@@ -56430,7 +56430,7 @@
         <v>0</v>
       </c>
       <c r="O562">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P562">
         <v>0</v>
@@ -56509,7 +56509,7 @@
         <v>0</v>
       </c>
       <c r="O563">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P563">
         <v>0</v>
@@ -56588,7 +56588,7 @@
         <v>0</v>
       </c>
       <c r="O564">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P564">
         <v>0</v>
@@ -56667,7 +56667,7 @@
         <v>0</v>
       </c>
       <c r="O565">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P565">
         <v>0</v>
@@ -56746,7 +56746,7 @@
         <v>0</v>
       </c>
       <c r="O566">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P566">
         <v>0</v>
@@ -56825,7 +56825,7 @@
         <v>0</v>
       </c>
       <c r="O567">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P567">
         <v>0</v>
@@ -56904,7 +56904,7 @@
         <v>0</v>
       </c>
       <c r="O568">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P568">
         <v>0</v>
@@ -56983,7 +56983,7 @@
         <v>0</v>
       </c>
       <c r="O569">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P569">
         <v>0</v>
@@ -57062,7 +57062,7 @@
         <v>0</v>
       </c>
       <c r="O570">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P570">
         <v>0</v>
@@ -57141,7 +57141,7 @@
         <v>0</v>
       </c>
       <c r="O571">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P571">
         <v>0</v>
@@ -57220,7 +57220,7 @@
         <v>0</v>
       </c>
       <c r="O572">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P572">
         <v>0</v>
@@ -57299,7 +57299,7 @@
         <v>0</v>
       </c>
       <c r="O573">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P573">
         <v>0</v>
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="O574">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P574">
         <v>0</v>
@@ -57457,7 +57457,7 @@
         <v>0</v>
       </c>
       <c r="O575">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P575">
         <v>0</v>
@@ -57536,7 +57536,7 @@
         <v>0</v>
       </c>
       <c r="O576">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P576">
         <v>0</v>
@@ -57615,7 +57615,7 @@
         <v>0</v>
       </c>
       <c r="O577">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P577">
         <v>0</v>
@@ -57694,7 +57694,7 @@
         <v>0</v>
       </c>
       <c r="O578">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P578">
         <v>0</v>
@@ -57773,7 +57773,7 @@
         <v>0</v>
       </c>
       <c r="O579">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P579">
         <v>0</v>
@@ -57852,7 +57852,7 @@
         <v>0</v>
       </c>
       <c r="O580">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P580">
         <v>0</v>
@@ -57931,7 +57931,7 @@
         <v>0</v>
       </c>
       <c r="O581">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P581">
         <v>0</v>
@@ -58010,7 +58010,7 @@
         <v>0</v>
       </c>
       <c r="O582">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P582">
         <v>0</v>
@@ -58089,7 +58089,7 @@
         <v>0</v>
       </c>
       <c r="O583">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P583">
         <v>0</v>
@@ -58168,7 +58168,7 @@
         <v>0</v>
       </c>
       <c r="O584">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P584">
         <v>0</v>
@@ -58247,7 +58247,7 @@
         <v>0</v>
       </c>
       <c r="O585">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P585">
         <v>0</v>
@@ -58326,7 +58326,7 @@
         <v>0</v>
       </c>
       <c r="O586">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P586">
         <v>0</v>
@@ -58405,7 +58405,7 @@
         <v>0</v>
       </c>
       <c r="O587">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P587">
         <v>0</v>
@@ -58484,7 +58484,7 @@
         <v>0</v>
       </c>
       <c r="O588">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P588">
         <v>0</v>
@@ -58563,7 +58563,7 @@
         <v>0</v>
       </c>
       <c r="O589">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P589">
         <v>0</v>
@@ -58642,7 +58642,7 @@
         <v>0</v>
       </c>
       <c r="O590">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P590">
         <v>0</v>
@@ -58721,7 +58721,7 @@
         <v>0</v>
       </c>
       <c r="O591">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P591">
         <v>0</v>
@@ -58800,7 +58800,7 @@
         <v>0</v>
       </c>
       <c r="O592">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P592">
         <v>0</v>
@@ -58879,7 +58879,7 @@
         <v>0</v>
       </c>
       <c r="O593">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P593">
         <v>0</v>
@@ -58958,7 +58958,7 @@
         <v>0</v>
       </c>
       <c r="O594">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P594">
         <v>0</v>
@@ -59037,7 +59037,7 @@
         <v>0</v>
       </c>
       <c r="O595">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P595">
         <v>0</v>
@@ -59116,7 +59116,7 @@
         <v>0</v>
       </c>
       <c r="O596">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P596">
         <v>0</v>
@@ -59192,7 +59192,7 @@
         <v>0</v>
       </c>
       <c r="O597">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P597">
         <v>0</v>
@@ -59271,7 +59271,7 @@
         <v>0</v>
       </c>
       <c r="O598">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P598">
         <v>0</v>
@@ -59350,7 +59350,7 @@
         <v>0</v>
       </c>
       <c r="O599">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P599">
         <v>0</v>
@@ -59429,7 +59429,7 @@
         <v>0</v>
       </c>
       <c r="O600">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P600">
         <v>0</v>
@@ -59508,7 +59508,7 @@
         <v>0</v>
       </c>
       <c r="O601">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P601">
         <v>0</v>
@@ -59587,7 +59587,7 @@
         <v>0</v>
       </c>
       <c r="O602">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P602">
         <v>0</v>
@@ -59666,7 +59666,7 @@
         <v>0</v>
       </c>
       <c r="O603">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P603">
         <v>0</v>
@@ -59745,7 +59745,7 @@
         <v>0</v>
       </c>
       <c r="O604">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P604">
         <v>0</v>
@@ -59824,7 +59824,7 @@
         <v>0</v>
       </c>
       <c r="O605">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P605">
         <v>0</v>
@@ -59903,7 +59903,7 @@
         <v>0</v>
       </c>
       <c r="O606">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P606">
         <v>0</v>
@@ -59982,7 +59982,7 @@
         <v>0</v>
       </c>
       <c r="O607">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P607">
         <v>0</v>
@@ -60061,7 +60061,7 @@
         <v>0</v>
       </c>
       <c r="O608">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P608">
         <v>0</v>
@@ -60140,7 +60140,7 @@
         <v>0</v>
       </c>
       <c r="O609">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P609">
         <v>0</v>
@@ -60219,7 +60219,7 @@
         <v>0</v>
       </c>
       <c r="O610">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P610">
         <v>0</v>
@@ -60298,7 +60298,7 @@
         <v>0</v>
       </c>
       <c r="O611">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P611">
         <v>0</v>
@@ -60377,7 +60377,7 @@
         <v>0</v>
       </c>
       <c r="O612">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P612">
         <v>0</v>
@@ -60456,7 +60456,7 @@
         <v>0</v>
       </c>
       <c r="O613">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P613">
         <v>0</v>
@@ -60535,7 +60535,7 @@
         <v>0</v>
       </c>
       <c r="O614">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P614">
         <v>0</v>
@@ -60611,7 +60611,7 @@
         <v>0</v>
       </c>
       <c r="O615">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P615">
         <v>0</v>
@@ -60690,7 +60690,7 @@
         <v>0</v>
       </c>
       <c r="O616">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P616">
         <v>0</v>
@@ -60769,7 +60769,7 @@
         <v>0</v>
       </c>
       <c r="O617">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P617">
         <v>0</v>
@@ -60848,7 +60848,7 @@
         <v>0</v>
       </c>
       <c r="O618">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P618">
         <v>0</v>
@@ -60927,7 +60927,7 @@
         <v>0</v>
       </c>
       <c r="O619">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P619">
         <v>0</v>
@@ -61003,7 +61003,7 @@
         <v>0</v>
       </c>
       <c r="O620">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P620">
         <v>0</v>
@@ -61082,7 +61082,7 @@
         <v>0</v>
       </c>
       <c r="O621">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P621">
         <v>0</v>
@@ -61161,7 +61161,7 @@
         <v>0</v>
       </c>
       <c r="O622">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P622">
         <v>0</v>
@@ -61240,7 +61240,7 @@
         <v>0</v>
       </c>
       <c r="O623">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P623">
         <v>0</v>
@@ -61319,7 +61319,7 @@
         <v>0</v>
       </c>
       <c r="O624">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P624">
         <v>0</v>
@@ -61398,7 +61398,7 @@
         <v>0</v>
       </c>
       <c r="O625">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P625">
         <v>0</v>
@@ -61477,7 +61477,7 @@
         <v>0</v>
       </c>
       <c r="O626">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P626">
         <v>0</v>
@@ -61556,7 +61556,7 @@
         <v>0</v>
       </c>
       <c r="O627">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P627">
         <v>0</v>
@@ -61635,7 +61635,7 @@
         <v>0</v>
       </c>
       <c r="O628">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P628">
         <v>0</v>
@@ -61714,7 +61714,7 @@
         <v>0</v>
       </c>
       <c r="O629">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P629">
         <v>0</v>
@@ -61793,7 +61793,7 @@
         <v>0</v>
       </c>
       <c r="O630">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P630">
         <v>0</v>
@@ -61872,7 +61872,7 @@
         <v>0</v>
       </c>
       <c r="O631">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P631">
         <v>0</v>
@@ -61951,7 +61951,7 @@
         <v>0</v>
       </c>
       <c r="O632">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P632">
         <v>0</v>
@@ -62027,10 +62027,10 @@
         <v>0</v>
       </c>
       <c r="N633">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O633">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P633">
         <v>0</v>
@@ -62109,7 +62109,7 @@
         <v>0</v>
       </c>
       <c r="O634">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P634">
         <v>0</v>
@@ -62188,7 +62188,7 @@
         <v>0</v>
       </c>
       <c r="O635">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P635">
         <v>0</v>
@@ -62267,7 +62267,7 @@
         <v>0</v>
       </c>
       <c r="O636">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P636">
         <v>0</v>
@@ -62346,7 +62346,7 @@
         <v>0</v>
       </c>
       <c r="O637">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P637">
         <v>0</v>
@@ -62425,7 +62425,7 @@
         <v>0</v>
       </c>
       <c r="O638">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P638">
         <v>0</v>
@@ -62504,7 +62504,7 @@
         <v>0</v>
       </c>
       <c r="O639">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P639">
         <v>0</v>
@@ -62580,7 +62580,7 @@
         <v>0</v>
       </c>
       <c r="N640">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O640">
         <v>0</v>
@@ -62741,7 +62741,7 @@
         <v>0</v>
       </c>
       <c r="O642">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="P642">
         <v>0</v>
@@ -62820,10 +62820,10 @@
         <v>0</v>
       </c>
       <c r="O643">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P643">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q643">
         <v>0</v>
@@ -62899,10 +62899,10 @@
         <v>0</v>
       </c>
       <c r="O644">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P644">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q644">
         <v>0</v>
@@ -62978,10 +62978,10 @@
         <v>0</v>
       </c>
       <c r="O645">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P645">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q645">
         <v>0</v>
@@ -63057,7 +63057,7 @@
         <v>0</v>
       </c>
       <c r="O646">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P646">
         <v>0</v>
@@ -63136,7 +63136,7 @@
         <v>0</v>
       </c>
       <c r="O647">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P647">
         <v>0</v>
@@ -63215,7 +63215,7 @@
         <v>0</v>
       </c>
       <c r="O648">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P648">
         <v>0</v>
@@ -63528,7 +63528,7 @@
         <v>0</v>
       </c>
       <c r="N652">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O652">
         <v>0</v>
@@ -63604,7 +63604,7 @@
         <v>0</v>
       </c>
       <c r="N653">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O653">
         <v>0</v>
@@ -63683,7 +63683,7 @@
         <v>0</v>
       </c>
       <c r="N654">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O654">
         <v>0</v>
@@ -63762,7 +63762,7 @@
         <v>0</v>
       </c>
       <c r="N655">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O655">
         <v>0</v>
@@ -63920,10 +63920,10 @@
         <v>0</v>
       </c>
       <c r="N657">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O657">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P657">
         <v>0</v>
@@ -63999,10 +63999,10 @@
         <v>0</v>
       </c>
       <c r="N658">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O658">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P658">
         <v>0</v>
@@ -64081,7 +64081,7 @@
         <v>0</v>
       </c>
       <c r="O659">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P659">
         <v>0</v>
@@ -64160,7 +64160,7 @@
         <v>0</v>
       </c>
       <c r="O660">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P660">
         <v>0</v>
@@ -64239,7 +64239,7 @@
         <v>0</v>
       </c>
       <c r="O661">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P661">
         <v>0</v>
@@ -64318,7 +64318,7 @@
         <v>0</v>
       </c>
       <c r="O662">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P662">
         <v>0</v>
@@ -64397,7 +64397,7 @@
         <v>0</v>
       </c>
       <c r="O663">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P663">
         <v>0</v>
@@ -64476,7 +64476,7 @@
         <v>0</v>
       </c>
       <c r="O664">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P664">
         <v>0</v>
@@ -64555,7 +64555,7 @@
         <v>0</v>
       </c>
       <c r="O665">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P665">
         <v>0</v>
@@ -64634,7 +64634,7 @@
         <v>0</v>
       </c>
       <c r="O666">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P666">
         <v>0</v>
@@ -64713,7 +64713,7 @@
         <v>0</v>
       </c>
       <c r="O667">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P667">
         <v>0</v>
@@ -64792,7 +64792,7 @@
         <v>0</v>
       </c>
       <c r="O668">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P668">
         <v>0</v>
@@ -64868,7 +64868,7 @@
         <v>0</v>
       </c>
       <c r="N669">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O669">
         <v>0</v>
@@ -64950,7 +64950,7 @@
         <v>0</v>
       </c>
       <c r="O670">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P670">
         <v>0</v>
@@ -65029,7 +65029,7 @@
         <v>0</v>
       </c>
       <c r="O671">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P671">
         <v>0</v>
@@ -65108,7 +65108,7 @@
         <v>0</v>
       </c>
       <c r="O672">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P672">
         <v>0</v>
@@ -65187,7 +65187,7 @@
         <v>0</v>
       </c>
       <c r="O673">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P673">
         <v>0</v>
@@ -65266,7 +65266,7 @@
         <v>0</v>
       </c>
       <c r="O674">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P674">
         <v>0</v>
@@ -65345,7 +65345,7 @@
         <v>0</v>
       </c>
       <c r="O675">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P675">
         <v>0</v>
@@ -65424,7 +65424,7 @@
         <v>0</v>
       </c>
       <c r="O676">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P676">
         <v>0</v>
@@ -65503,7 +65503,7 @@
         <v>0</v>
       </c>
       <c r="O677">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P677">
         <v>0</v>
@@ -65582,7 +65582,7 @@
         <v>0</v>
       </c>
       <c r="O678">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P678">
         <v>0</v>
@@ -65737,10 +65737,10 @@
         <v>0</v>
       </c>
       <c r="N680">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O680">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P680">
         <v>0</v>
@@ -65816,10 +65816,10 @@
         <v>0</v>
       </c>
       <c r="N681">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O681">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P681">
         <v>0</v>
@@ -65898,7 +65898,7 @@
         <v>0</v>
       </c>
       <c r="O682">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P682">
         <v>0</v>
@@ -65977,7 +65977,7 @@
         <v>0</v>
       </c>
       <c r="O683">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P683">
         <v>0</v>
@@ -66056,7 +66056,7 @@
         <v>0</v>
       </c>
       <c r="O684">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P684">
         <v>0</v>
@@ -66135,7 +66135,7 @@
         <v>0</v>
       </c>
       <c r="O685">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P685">
         <v>0</v>
@@ -66214,7 +66214,7 @@
         <v>0</v>
       </c>
       <c r="O686">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P686">
         <v>0</v>
@@ -66290,7 +66290,7 @@
         <v>0</v>
       </c>
       <c r="N687">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O687">
         <v>0</v>
@@ -66764,7 +66764,7 @@
         <v>0</v>
       </c>
       <c r="N693">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O693">
         <v>0</v>
@@ -67001,7 +67001,7 @@
         <v>0</v>
       </c>
       <c r="N696">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O696">
         <v>0</v>
@@ -67080,7 +67080,7 @@
         <v>0</v>
       </c>
       <c r="N697">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O697">
         <v>0</v>
@@ -67156,7 +67156,7 @@
         <v>0</v>
       </c>
       <c r="N698">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O698">
         <v>0</v>
@@ -67235,7 +67235,7 @@
         <v>0</v>
       </c>
       <c r="O699">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P699">
         <v>0</v>
@@ -67311,7 +67311,7 @@
         <v>0</v>
       </c>
       <c r="N700">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O700">
         <v>0</v>
@@ -67393,7 +67393,7 @@
         <v>0</v>
       </c>
       <c r="O701">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P701">
         <v>0</v>
@@ -67548,13 +67548,13 @@
         <v>2</v>
       </c>
       <c r="N703">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O703">
         <v>0</v>
       </c>
       <c r="P703">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q703">
         <v>0</v>
@@ -67706,7 +67706,7 @@
         <v>0</v>
       </c>
       <c r="N705">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O705">
         <v>0</v>
@@ -67785,7 +67785,7 @@
         <v>0</v>
       </c>
       <c r="N706">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O706">
         <v>0</v>
@@ -67864,7 +67864,7 @@
         <v>0</v>
       </c>
       <c r="N707">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O707">
         <v>0</v>
@@ -68022,7 +68022,7 @@
         <v>0</v>
       </c>
       <c r="N709">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O709">
         <v>0</v>
@@ -68101,7 +68101,7 @@
         <v>0</v>
       </c>
       <c r="N710">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O710">
         <v>0</v>
@@ -68180,7 +68180,7 @@
         <v>0</v>
       </c>
       <c r="N711">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O711">
         <v>0</v>
@@ -68259,7 +68259,7 @@
         <v>0</v>
       </c>
       <c r="N712">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O712">
         <v>0</v>
@@ -68338,7 +68338,7 @@
         <v>0</v>
       </c>
       <c r="N713">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O713">
         <v>0</v>
@@ -68417,7 +68417,7 @@
         <v>0</v>
       </c>
       <c r="N714">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O714">
         <v>0</v>
@@ -68493,7 +68493,7 @@
         <v>0</v>
       </c>
       <c r="N715">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O715">
         <v>0</v>
@@ -68572,7 +68572,7 @@
         <v>0</v>
       </c>
       <c r="N716">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O716">
         <v>0</v>
@@ -68651,7 +68651,7 @@
         <v>0</v>
       </c>
       <c r="N717">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O717">
         <v>0</v>
@@ -68727,7 +68727,7 @@
         <v>0</v>
       </c>
       <c r="N718">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O718">
         <v>0</v>
@@ -68806,7 +68806,7 @@
         <v>0</v>
       </c>
       <c r="N719">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O719">
         <v>0</v>
@@ -68885,7 +68885,7 @@
         <v>0</v>
       </c>
       <c r="N720">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O720">
         <v>0</v>
@@ -68964,7 +68964,7 @@
         <v>0</v>
       </c>
       <c r="N721">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O721">
         <v>0</v>
@@ -69043,10 +69043,10 @@
         <v>0</v>
       </c>
       <c r="N722">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O722">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P722">
         <v>0</v>
@@ -69122,7 +69122,7 @@
         <v>0</v>
       </c>
       <c r="N723">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O723">
         <v>0</v>
@@ -69201,7 +69201,7 @@
         <v>0</v>
       </c>
       <c r="N724">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O724">
         <v>0</v>
@@ -69280,7 +69280,7 @@
         <v>0</v>
       </c>
       <c r="N725">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O725">
         <v>0</v>
@@ -69359,7 +69359,7 @@
         <v>0</v>
       </c>
       <c r="N726">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O726">
         <v>0</v>
@@ -69438,7 +69438,7 @@
         <v>0</v>
       </c>
       <c r="N727">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O727">
         <v>0</v>
@@ -69517,7 +69517,7 @@
         <v>0</v>
       </c>
       <c r="N728">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O728">
         <v>0</v>
@@ -69596,7 +69596,7 @@
         <v>0</v>
       </c>
       <c r="N729">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O729">
         <v>0</v>
@@ -69675,7 +69675,7 @@
         <v>0</v>
       </c>
       <c r="N730">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O730">
         <v>0</v>
@@ -69754,7 +69754,7 @@
         <v>0</v>
       </c>
       <c r="N731">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O731">
         <v>0</v>
@@ -69833,7 +69833,7 @@
         <v>0</v>
       </c>
       <c r="N732">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O732">
         <v>0</v>
@@ -69912,7 +69912,7 @@
         <v>0</v>
       </c>
       <c r="N733">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O733">
         <v>0</v>
@@ -69991,7 +69991,7 @@
         <v>0</v>
       </c>
       <c r="N734">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O734">
         <v>0</v>
@@ -70070,7 +70070,7 @@
         <v>0</v>
       </c>
       <c r="N735">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O735">
         <v>0</v>
@@ -70146,10 +70146,10 @@
         <v>0</v>
       </c>
       <c r="N736">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O736">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P736">
         <v>0</v>
@@ -70225,7 +70225,7 @@
         <v>0</v>
       </c>
       <c r="N737">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O737">
         <v>0</v>
@@ -70304,7 +70304,7 @@
         <v>0</v>
       </c>
       <c r="N738">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O738">
         <v>0</v>
@@ -70383,7 +70383,7 @@
         <v>0</v>
       </c>
       <c r="N739">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O739">
         <v>0</v>
@@ -70462,7 +70462,7 @@
         <v>0</v>
       </c>
       <c r="N740">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O740">
         <v>0</v>
@@ -70541,7 +70541,7 @@
         <v>0</v>
       </c>
       <c r="N741">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O741">
         <v>0</v>
@@ -70620,10 +70620,10 @@
         <v>0</v>
       </c>
       <c r="N742">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O742">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P742">
         <v>0</v>
@@ -70699,7 +70699,7 @@
         <v>0</v>
       </c>
       <c r="N743">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O743">
         <v>0</v>
@@ -70778,7 +70778,7 @@
         <v>0</v>
       </c>
       <c r="N744">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O744">
         <v>0</v>
@@ -70857,13 +70857,13 @@
         <v>1</v>
       </c>
       <c r="N745">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O745">
         <v>0</v>
       </c>
       <c r="P745">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q745">
         <v>0</v>
@@ -70936,7 +70936,7 @@
         <v>0</v>
       </c>
       <c r="N746">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O746">
         <v>0</v>
@@ -71015,7 +71015,7 @@
         <v>0</v>
       </c>
       <c r="N747">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O747">
         <v>0</v>
@@ -71091,7 +71091,7 @@
         <v>0</v>
       </c>
       <c r="N748">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O748">
         <v>0</v>
@@ -71173,7 +71173,7 @@
         <v>0</v>
       </c>
       <c r="O749">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P749">
         <v>0</v>
@@ -71328,10 +71328,10 @@
         <v>0</v>
       </c>
       <c r="N751">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O751">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P751">
         <v>0</v>
@@ -71407,7 +71407,7 @@
         <v>0</v>
       </c>
       <c r="N752">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O752">
         <v>0</v>
@@ -71486,7 +71486,7 @@
         <v>0</v>
       </c>
       <c r="N753">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O753">
         <v>0</v>
@@ -71565,7 +71565,7 @@
         <v>0</v>
       </c>
       <c r="N754">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O754">
         <v>0</v>
@@ -71644,7 +71644,7 @@
         <v>0</v>
       </c>
       <c r="N755">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O755">
         <v>0</v>
@@ -71723,7 +71723,7 @@
         <v>0</v>
       </c>
       <c r="N756">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O756">
         <v>0</v>
@@ -71802,7 +71802,7 @@
         <v>0</v>
       </c>
       <c r="N757">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O757">
         <v>0</v>
@@ -71881,7 +71881,7 @@
         <v>0</v>
       </c>
       <c r="N758">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O758">
         <v>0</v>
@@ -71960,7 +71960,7 @@
         <v>0</v>
       </c>
       <c r="N759">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O759">
         <v>0</v>
@@ -72039,7 +72039,7 @@
         <v>0</v>
       </c>
       <c r="N760">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O760">
         <v>0</v>
@@ -72118,7 +72118,7 @@
         <v>0</v>
       </c>
       <c r="N761">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O761">
         <v>0</v>
@@ -72197,7 +72197,7 @@
         <v>0</v>
       </c>
       <c r="N762">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O762">
         <v>0</v>
@@ -72276,7 +72276,7 @@
         <v>0</v>
       </c>
       <c r="N763">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O763">
         <v>0</v>
@@ -72437,7 +72437,7 @@
         <v>0</v>
       </c>
       <c r="O765">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P765">
         <v>0</v>
@@ -72516,7 +72516,7 @@
         <v>0</v>
       </c>
       <c r="O766">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P766">
         <v>0</v>
@@ -72595,7 +72595,7 @@
         <v>0</v>
       </c>
       <c r="O767">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P767">
         <v>0</v>
@@ -72674,7 +72674,7 @@
         <v>0</v>
       </c>
       <c r="O768">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P768">
         <v>0</v>
@@ -72753,7 +72753,7 @@
         <v>0</v>
       </c>
       <c r="O769">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P769">
         <v>0</v>
@@ -72829,10 +72829,10 @@
         <v>0</v>
       </c>
       <c r="N770">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O770">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P770">
         <v>0</v>
@@ -72911,7 +72911,7 @@
         <v>0</v>
       </c>
       <c r="O771">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P771">
         <v>0</v>
@@ -72990,7 +72990,7 @@
         <v>0</v>
       </c>
       <c r="O772">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P772">
         <v>0</v>
@@ -73069,7 +73069,7 @@
         <v>0</v>
       </c>
       <c r="O773">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P773">
         <v>0</v>
@@ -73148,7 +73148,7 @@
         <v>0</v>
       </c>
       <c r="O774">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P774">
         <v>0</v>
@@ -73227,7 +73227,7 @@
         <v>0</v>
       </c>
       <c r="O775">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P775">
         <v>0</v>
@@ -73306,7 +73306,7 @@
         <v>0</v>
       </c>
       <c r="O776">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P776">
         <v>0</v>
@@ -73385,7 +73385,7 @@
         <v>0</v>
       </c>
       <c r="O777">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P777">
         <v>0</v>
@@ -73464,7 +73464,7 @@
         <v>0</v>
       </c>
       <c r="O778">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P778">
         <v>0</v>
@@ -73543,7 +73543,7 @@
         <v>0</v>
       </c>
       <c r="O779">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P779">
         <v>0</v>
@@ -73622,7 +73622,7 @@
         <v>0</v>
       </c>
       <c r="O780">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P780">
         <v>0</v>
@@ -73701,7 +73701,7 @@
         <v>0</v>
       </c>
       <c r="O781">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P781">
         <v>0</v>
@@ -73780,7 +73780,7 @@
         <v>0</v>
       </c>
       <c r="O782">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P782">
         <v>0</v>
@@ -73859,7 +73859,7 @@
         <v>0</v>
       </c>
       <c r="O783">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P783">
         <v>0</v>
@@ -73938,7 +73938,7 @@
         <v>0</v>
       </c>
       <c r="O784">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P784">
         <v>0</v>
@@ -74014,10 +74014,10 @@
         <v>0</v>
       </c>
       <c r="N785">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O785">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P785">
         <v>0</v>
@@ -74096,7 +74096,7 @@
         <v>0</v>
       </c>
       <c r="O786">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P786">
         <v>0</v>
@@ -74175,7 +74175,7 @@
         <v>0</v>
       </c>
       <c r="O787">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P787">
         <v>0</v>
@@ -74254,7 +74254,7 @@
         <v>0</v>
       </c>
       <c r="O788">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P788">
         <v>0</v>
@@ -74333,7 +74333,7 @@
         <v>0</v>
       </c>
       <c r="O789">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P789">
         <v>0</v>
@@ -74412,7 +74412,7 @@
         <v>0</v>
       </c>
       <c r="O790">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P790">
         <v>0</v>
@@ -74491,7 +74491,7 @@
         <v>0</v>
       </c>
       <c r="O791">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P791">
         <v>0</v>
@@ -74567,7 +74567,7 @@
         <v>0</v>
       </c>
       <c r="N792">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O792">
         <v>0</v>
@@ -74725,7 +74725,7 @@
         <v>0</v>
       </c>
       <c r="N794">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O794">
         <v>0</v>
@@ -74804,7 +74804,7 @@
         <v>0</v>
       </c>
       <c r="N795">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O795">
         <v>0</v>
@@ -74962,7 +74962,7 @@
         <v>0</v>
       </c>
       <c r="N797">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O797">
         <v>0</v>
@@ -75120,7 +75120,7 @@
         <v>0</v>
       </c>
       <c r="N799">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O799">
         <v>0</v>
@@ -75199,7 +75199,7 @@
         <v>0</v>
       </c>
       <c r="N800">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O800">
         <v>0</v>
@@ -75439,7 +75439,7 @@
         <v>0</v>
       </c>
       <c r="O803">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P803">
         <v>0</v>
@@ -75594,7 +75594,7 @@
         <v>0</v>
       </c>
       <c r="N805">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O805">
         <v>0</v>
@@ -75755,7 +75755,7 @@
         <v>0</v>
       </c>
       <c r="O807">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="P807">
         <v>0</v>
@@ -75834,7 +75834,7 @@
         <v>0</v>
       </c>
       <c r="O808">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="P808">
         <v>0</v>
@@ -75907,10 +75907,10 @@
         <v>0</v>
       </c>
       <c r="N809">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O809">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P809">
         <v>0</v>
@@ -75989,7 +75989,7 @@
         <v>0</v>
       </c>
       <c r="O810">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P810">
         <v>0</v>
@@ -76068,7 +76068,7 @@
         <v>0</v>
       </c>
       <c r="O811">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P811">
         <v>0</v>
@@ -76147,7 +76147,7 @@
         <v>0</v>
       </c>
       <c r="O812">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P812">
         <v>0</v>
@@ -76226,7 +76226,7 @@
         <v>0</v>
       </c>
       <c r="O813">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P813">
         <v>0</v>
@@ -76305,7 +76305,7 @@
         <v>0</v>
       </c>
       <c r="O814">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P814">
         <v>0</v>
@@ -76384,7 +76384,7 @@
         <v>0</v>
       </c>
       <c r="O815">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P815">
         <v>0</v>
@@ -76463,7 +76463,7 @@
         <v>0</v>
       </c>
       <c r="O816">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P816">
         <v>0</v>
@@ -76542,7 +76542,7 @@
         <v>0</v>
       </c>
       <c r="O817">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P817">
         <v>0</v>
@@ -76621,7 +76621,7 @@
         <v>0</v>
       </c>
       <c r="O818">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P818">
         <v>0</v>
@@ -76700,7 +76700,7 @@
         <v>0</v>
       </c>
       <c r="O819">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="P819">
         <v>0</v>
@@ -76779,7 +76779,7 @@
         <v>0</v>
       </c>
       <c r="O820">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P820">
         <v>0</v>
@@ -76858,7 +76858,7 @@
         <v>0</v>
       </c>
       <c r="O821">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P821">
         <v>0</v>
@@ -76937,7 +76937,7 @@
         <v>0</v>
       </c>
       <c r="O822">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P822">
         <v>0</v>
@@ -77016,7 +77016,7 @@
         <v>0</v>
       </c>
       <c r="O823">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P823">
         <v>0</v>
@@ -77095,7 +77095,7 @@
         <v>0</v>
       </c>
       <c r="O824">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P824">
         <v>0</v>
@@ -77174,7 +77174,7 @@
         <v>0</v>
       </c>
       <c r="O825">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P825">
         <v>0</v>
@@ -77250,10 +77250,10 @@
         <v>0</v>
       </c>
       <c r="N826">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="O826">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="P826">
         <v>0</v>
@@ -77326,10 +77326,10 @@
         <v>0</v>
       </c>
       <c r="N827">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="O827">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="P827">
         <v>0</v>
@@ -77402,10 +77402,10 @@
         <v>0</v>
       </c>
       <c r="N828">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="O828">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="P828">
         <v>0</v>
@@ -77481,10 +77481,10 @@
         <v>0</v>
       </c>
       <c r="N829">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="O829">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P829">
         <v>0</v>
@@ -77560,10 +77560,10 @@
         <v>0</v>
       </c>
       <c r="N830">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="O830">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P830">
         <v>0</v>
@@ -77639,10 +77639,10 @@
         <v>0</v>
       </c>
       <c r="N831">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O831">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P831">
         <v>0</v>
@@ -77718,13 +77718,13 @@
         <v>1</v>
       </c>
       <c r="N832">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O832">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P832">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q832">
         <v>0</v>
@@ -77797,7 +77797,7 @@
         <v>0</v>
       </c>
       <c r="N833">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="O833">
         <v>0</v>
@@ -77876,7 +77876,7 @@
         <v>0</v>
       </c>
       <c r="N834">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="O834">
         <v>0</v>
@@ -77955,7 +77955,7 @@
         <v>0</v>
       </c>
       <c r="N835">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O835">
         <v>0</v>
@@ -78034,10 +78034,10 @@
         <v>0</v>
       </c>
       <c r="N836">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="O836">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="P836">
         <v>0</v>
@@ -78110,10 +78110,10 @@
         <v>0</v>
       </c>
       <c r="N837">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="O837">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="P837">
         <v>0</v>
@@ -78186,7 +78186,7 @@
         <v>0</v>
       </c>
       <c r="N838">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="O838">
         <v>0</v>
@@ -78265,10 +78265,10 @@
         <v>0</v>
       </c>
       <c r="N839">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="O839">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P839">
         <v>0</v>
@@ -78344,10 +78344,10 @@
         <v>0</v>
       </c>
       <c r="N840">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="O840">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="P840">
         <v>0</v>
@@ -78423,10 +78423,10 @@
         <v>0</v>
       </c>
       <c r="N841">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="O841">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P841">
         <v>0</v>
@@ -78499,7 +78499,7 @@
         <v>0</v>
       </c>
       <c r="N842">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="O842">
         <v>0</v>
@@ -78578,10 +78578,10 @@
         <v>0</v>
       </c>
       <c r="N843">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="O843">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="P843">
         <v>0</v>
@@ -78654,7 +78654,7 @@
         <v>0</v>
       </c>
       <c r="N844">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="O844">
         <v>0</v>
@@ -78733,7 +78733,7 @@
         <v>0</v>
       </c>
       <c r="N845">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="O845">
         <v>0</v>
@@ -78812,7 +78812,7 @@
         <v>0</v>
       </c>
       <c r="N846">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O846">
         <v>0</v>
@@ -78891,7 +78891,7 @@
         <v>0</v>
       </c>
       <c r="N847">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O847">
         <v>0</v>
@@ -78973,7 +78973,7 @@
         <v>0</v>
       </c>
       <c r="O848">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P848">
         <v>0</v>
@@ -79125,7 +79125,7 @@
         <v>0</v>
       </c>
       <c r="O850">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="P850">
         <v>0</v>
@@ -79204,7 +79204,7 @@
         <v>0</v>
       </c>
       <c r="O851">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="P851">
         <v>0</v>
@@ -79280,10 +79280,10 @@
         <v>0</v>
       </c>
       <c r="N852">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O852">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P852">
         <v>0</v>
@@ -79362,7 +79362,7 @@
         <v>0</v>
       </c>
       <c r="O853">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P853">
         <v>0</v>
@@ -79441,7 +79441,7 @@
         <v>0</v>
       </c>
       <c r="O854">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P854">
         <v>0</v>
@@ -79517,10 +79517,10 @@
         <v>0</v>
       </c>
       <c r="N855">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O855">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="P855">
         <v>0</v>
@@ -79596,10 +79596,10 @@
         <v>0</v>
       </c>
       <c r="N856">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O856">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="P856">
         <v>0</v>
@@ -79675,13 +79675,13 @@
         <v>1</v>
       </c>
       <c r="N857">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O857">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P857">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q857">
         <v>0</v>
@@ -79754,10 +79754,10 @@
         <v>0</v>
       </c>
       <c r="N858">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O858">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P858">
         <v>0</v>
@@ -79833,10 +79833,10 @@
         <v>0</v>
       </c>
       <c r="N859">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O859">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P859">
         <v>0</v>
@@ -79912,10 +79912,10 @@
         <v>0</v>
       </c>
       <c r="N860">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O860">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P860">
         <v>0</v>
@@ -79991,10 +79991,10 @@
         <v>0</v>
       </c>
       <c r="N861">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O861">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P861">
         <v>0</v>
@@ -80070,10 +80070,10 @@
         <v>0</v>
       </c>
       <c r="N862">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O862">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="P862">
         <v>0</v>
@@ -80149,10 +80149,10 @@
         <v>0</v>
       </c>
       <c r="N863">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O863">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="P863">
         <v>0</v>
@@ -80231,7 +80231,7 @@
         <v>0</v>
       </c>
       <c r="O864">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="P864">
         <v>0</v>
@@ -80310,7 +80310,7 @@
         <v>0</v>
       </c>
       <c r="O865">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="P865">
         <v>0</v>
@@ -80386,10 +80386,10 @@
         <v>0</v>
       </c>
       <c r="N866">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O866">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="P866">
         <v>0</v>
@@ -80465,10 +80465,10 @@
         <v>0</v>
       </c>
       <c r="N867">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O867">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="P867">
         <v>0</v>
@@ -80544,10 +80544,10 @@
         <v>0</v>
       </c>
       <c r="N868">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O868">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P868">
         <v>0</v>
@@ -80623,10 +80623,10 @@
         <v>0</v>
       </c>
       <c r="N869">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O869">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="P869">
         <v>0</v>
@@ -80702,7 +80702,7 @@
         <v>0</v>
       </c>
       <c r="N870">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O870">
         <v>0</v>
@@ -80781,7 +80781,7 @@
         <v>0</v>
       </c>
       <c r="N871">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O871">
         <v>0</v>
@@ -80942,7 +80942,7 @@
         <v>0</v>
       </c>
       <c r="O873">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P873">
         <v>0</v>
@@ -81018,7 +81018,7 @@
         <v>0</v>
       </c>
       <c r="N874">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O874">
         <v>0</v>
@@ -81097,7 +81097,7 @@
         <v>0</v>
       </c>
       <c r="N875">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O875">
         <v>0</v>
@@ -81176,7 +81176,7 @@
         <v>0</v>
       </c>
       <c r="N876">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O876">
         <v>0</v>
@@ -81258,7 +81258,7 @@
         <v>0</v>
       </c>
       <c r="O877">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P877">
         <v>0</v>
@@ -81416,7 +81416,7 @@
         <v>0</v>
       </c>
       <c r="O879">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P879">
         <v>0</v>
@@ -81495,7 +81495,7 @@
         <v>0</v>
       </c>
       <c r="O880">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P880">
         <v>0</v>
@@ -81574,7 +81574,7 @@
         <v>0</v>
       </c>
       <c r="O881">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P881">
         <v>0</v>
@@ -81653,7 +81653,7 @@
         <v>0</v>
       </c>
       <c r="O882">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P882">
         <v>0</v>
@@ -81732,7 +81732,7 @@
         <v>0</v>
       </c>
       <c r="O883">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P883">
         <v>0</v>
@@ -81811,7 +81811,7 @@
         <v>0</v>
       </c>
       <c r="O884">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P884">
         <v>0</v>
@@ -81890,7 +81890,7 @@
         <v>0</v>
       </c>
       <c r="O885">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P885">
         <v>0</v>
@@ -81969,7 +81969,7 @@
         <v>0</v>
       </c>
       <c r="O886">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P886">
         <v>0</v>
@@ -82048,7 +82048,7 @@
         <v>0</v>
       </c>
       <c r="O887">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P887">
         <v>0</v>
@@ -82127,7 +82127,7 @@
         <v>0</v>
       </c>
       <c r="O888">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P888">
         <v>0</v>
@@ -82206,7 +82206,7 @@
         <v>0</v>
       </c>
       <c r="O889">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P889">
         <v>0</v>
@@ -82361,7 +82361,7 @@
         <v>0</v>
       </c>
       <c r="O891">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P891">
         <v>0</v>
@@ -82440,7 +82440,7 @@
         <v>0</v>
       </c>
       <c r="O892">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P892">
         <v>0</v>
@@ -82519,7 +82519,7 @@
         <v>0</v>
       </c>
       <c r="O893">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P893">
         <v>0</v>
@@ -82598,7 +82598,7 @@
         <v>0</v>
       </c>
       <c r="O894">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P894">
         <v>0</v>
@@ -82677,7 +82677,7 @@
         <v>0</v>
       </c>
       <c r="O895">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P895">
         <v>0</v>
@@ -82756,7 +82756,7 @@
         <v>0</v>
       </c>
       <c r="O896">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P896">
         <v>0</v>
@@ -82835,7 +82835,7 @@
         <v>0</v>
       </c>
       <c r="O897">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P897">
         <v>0</v>
@@ -82908,7 +82908,7 @@
         <v>0</v>
       </c>
       <c r="N898">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O898">
         <v>0</v>
@@ -82990,7 +82990,7 @@
         <v>0</v>
       </c>
       <c r="O899">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P899">
         <v>0</v>
@@ -83069,7 +83069,7 @@
         <v>0</v>
       </c>
       <c r="O900">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P900">
         <v>0</v>
@@ -83148,7 +83148,7 @@
         <v>0</v>
       </c>
       <c r="O901">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P901">
         <v>0</v>
@@ -83227,7 +83227,7 @@
         <v>0</v>
       </c>
       <c r="O902">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P902">
         <v>0</v>
@@ -83306,7 +83306,7 @@
         <v>0</v>
       </c>
       <c r="O903">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P903">
         <v>0</v>
@@ -83382,10 +83382,10 @@
         <v>0</v>
       </c>
       <c r="N904">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O904">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P904">
         <v>0</v>
@@ -83464,7 +83464,7 @@
         <v>0</v>
       </c>
       <c r="O905">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P905">
         <v>0</v>
@@ -83540,7 +83540,7 @@
         <v>0</v>
       </c>
       <c r="O906">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P906">
         <v>0</v>
@@ -83619,7 +83619,7 @@
         <v>0</v>
       </c>
       <c r="O907">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P907">
         <v>0</v>
@@ -83695,7 +83695,7 @@
         <v>0</v>
       </c>
       <c r="O908">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P908">
         <v>0</v>
@@ -83774,10 +83774,10 @@
         <v>0</v>
       </c>
       <c r="O909">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P909">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q909">
         <v>0</v>
@@ -83850,10 +83850,10 @@
         <v>0</v>
       </c>
       <c r="N910">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O910">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P910">
         <v>0</v>
@@ -83932,7 +83932,7 @@
         <v>0</v>
       </c>
       <c r="O911">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P911">
         <v>0</v>
@@ -84008,10 +84008,10 @@
         <v>0</v>
       </c>
       <c r="N912">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O912">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P912">
         <v>0</v>
@@ -84087,10 +84087,10 @@
         <v>0</v>
       </c>
       <c r="N913">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O913">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P913">
         <v>0</v>
@@ -84169,7 +84169,7 @@
         <v>0</v>
       </c>
       <c r="O914">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P914">
         <v>0</v>
@@ -84248,7 +84248,7 @@
         <v>0</v>
       </c>
       <c r="O915">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P915">
         <v>0</v>
@@ -84327,7 +84327,7 @@
         <v>0</v>
       </c>
       <c r="O916">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P916">
         <v>0</v>
@@ -84406,7 +84406,7 @@
         <v>0</v>
       </c>
       <c r="O917">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P917">
         <v>0</v>
@@ -84485,7 +84485,7 @@
         <v>0</v>
       </c>
       <c r="O918">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P918">
         <v>0</v>
@@ -84564,7 +84564,7 @@
         <v>0</v>
       </c>
       <c r="O919">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P919">
         <v>0</v>
@@ -84643,7 +84643,7 @@
         <v>0</v>
       </c>
       <c r="O920">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P920">
         <v>0</v>
@@ -84722,7 +84722,7 @@
         <v>0</v>
       </c>
       <c r="O921">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P921">
         <v>0</v>
@@ -84801,7 +84801,7 @@
         <v>0</v>
       </c>
       <c r="O922">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P922">
         <v>0</v>
@@ -84880,7 +84880,7 @@
         <v>0</v>
       </c>
       <c r="O923">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P923">
         <v>0</v>
@@ -84956,10 +84956,10 @@
         <v>0</v>
       </c>
       <c r="N924">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O924">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="P924">
         <v>0</v>
@@ -85035,10 +85035,10 @@
         <v>0</v>
       </c>
       <c r="N925">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O925">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="P925">
         <v>0</v>
@@ -85114,10 +85114,10 @@
         <v>0</v>
       </c>
       <c r="N926">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O926">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="P926">
         <v>0</v>
@@ -85196,7 +85196,7 @@
         <v>0</v>
       </c>
       <c r="O927">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="P927">
         <v>0</v>
@@ -85272,10 +85272,10 @@
         <v>0</v>
       </c>
       <c r="N928">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O928">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="P928">
         <v>0</v>
@@ -85351,10 +85351,10 @@
         <v>0</v>
       </c>
       <c r="N929">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O929">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="P929">
         <v>0</v>
@@ -85430,10 +85430,10 @@
         <v>0</v>
       </c>
       <c r="N930">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O930">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="P930">
         <v>0</v>
@@ -85512,7 +85512,7 @@
         <v>0</v>
       </c>
       <c r="O931">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="P931">
         <v>0</v>
@@ -85588,10 +85588,10 @@
         <v>0</v>
       </c>
       <c r="N932">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O932">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="P932">
         <v>0</v>
@@ -85667,10 +85667,10 @@
         <v>0</v>
       </c>
       <c r="N933">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O933">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P933">
         <v>0</v>
@@ -85746,10 +85746,10 @@
         <v>0</v>
       </c>
       <c r="N934">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O934">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P934">
         <v>0</v>
@@ -85825,10 +85825,10 @@
         <v>0</v>
       </c>
       <c r="N935">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O935">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="P935">
         <v>0</v>
@@ -85904,10 +85904,10 @@
         <v>0</v>
       </c>
       <c r="N936">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O936">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="P936">
         <v>0</v>
@@ -85983,10 +85983,10 @@
         <v>0</v>
       </c>
       <c r="N937">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O937">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="P937">
         <v>0</v>
@@ -86065,7 +86065,7 @@
         <v>0</v>
       </c>
       <c r="O938">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="P938">
         <v>0</v>
@@ -86141,10 +86141,10 @@
         <v>0</v>
       </c>
       <c r="N939">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O939">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="P939">
         <v>0</v>
@@ -86223,7 +86223,7 @@
         <v>0</v>
       </c>
       <c r="O940">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="P940">
         <v>0</v>
@@ -86302,7 +86302,7 @@
         <v>0</v>
       </c>
       <c r="O941">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="P941">
         <v>0</v>
@@ -86381,7 +86381,7 @@
         <v>0</v>
       </c>
       <c r="O942">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="P942">
         <v>0</v>
@@ -86457,10 +86457,10 @@
         <v>0</v>
       </c>
       <c r="N943">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O943">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="P943">
         <v>0</v>
@@ -86536,7 +86536,7 @@
         <v>0</v>
       </c>
       <c r="N944">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O944">
         <v>0</v>
@@ -86697,7 +86697,7 @@
         <v>0</v>
       </c>
       <c r="O946">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="P946">
         <v>0</v>
@@ -86776,7 +86776,7 @@
         <v>0</v>
       </c>
       <c r="O947">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="P947">
         <v>0</v>
@@ -86855,7 +86855,7 @@
         <v>0</v>
       </c>
       <c r="O948">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P948">
         <v>0</v>
@@ -86934,7 +86934,7 @@
         <v>0</v>
       </c>
       <c r="O949">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="P949">
         <v>0</v>
@@ -87013,7 +87013,7 @@
         <v>0</v>
       </c>
       <c r="O950">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P950">
         <v>0</v>
@@ -87092,7 +87092,7 @@
         <v>0</v>
       </c>
       <c r="O951">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P951">
         <v>0</v>
@@ -87171,7 +87171,7 @@
         <v>0</v>
       </c>
       <c r="O952">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P952">
         <v>0</v>
@@ -87329,7 +87329,7 @@
         <v>0</v>
       </c>
       <c r="O954">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="P954">
         <v>0</v>
@@ -87408,7 +87408,7 @@
         <v>0</v>
       </c>
       <c r="O955">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="P955">
         <v>0</v>
@@ -87484,10 +87484,10 @@
         <v>0</v>
       </c>
       <c r="N956">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O956">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="P956">
         <v>0</v>
@@ -87566,7 +87566,7 @@
         <v>0</v>
       </c>
       <c r="O957">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="P957">
         <v>0</v>
@@ -87645,7 +87645,7 @@
         <v>0</v>
       </c>
       <c r="O958">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="P958">
         <v>0</v>
@@ -87724,7 +87724,7 @@
         <v>0</v>
       </c>
       <c r="O959">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="P959">
         <v>0</v>
@@ -87803,7 +87803,7 @@
         <v>0</v>
       </c>
       <c r="O960">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P960">
         <v>0</v>
@@ -87879,10 +87879,10 @@
         <v>0</v>
       </c>
       <c r="N961">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O961">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P961">
         <v>0</v>
@@ -87958,7 +87958,7 @@
         <v>0</v>
       </c>
       <c r="N962">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O962">
         <v>0</v>
@@ -88037,7 +88037,7 @@
         <v>0</v>
       </c>
       <c r="N963">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O963">
         <v>0</v>
@@ -88116,7 +88116,7 @@
         <v>0</v>
       </c>
       <c r="N964">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O964">
         <v>0</v>
@@ -88195,7 +88195,7 @@
         <v>0</v>
       </c>
       <c r="N965">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O965">
         <v>0</v>
@@ -88274,7 +88274,7 @@
         <v>0</v>
       </c>
       <c r="N966">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O966">
         <v>0</v>
@@ -88353,7 +88353,7 @@
         <v>0</v>
       </c>
       <c r="N967">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O967">
         <v>0</v>
@@ -88432,7 +88432,7 @@
         <v>0</v>
       </c>
       <c r="N968">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O968">
         <v>0</v>
@@ -88669,7 +88669,7 @@
         <v>0</v>
       </c>
       <c r="N971">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="O971">
         <v>0</v>
@@ -88748,7 +88748,7 @@
         <v>0</v>
       </c>
       <c r="N972">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="O972">
         <v>0</v>
@@ -88827,7 +88827,7 @@
         <v>0</v>
       </c>
       <c r="N973">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O973">
         <v>0</v>
@@ -88982,7 +88982,7 @@
         <v>0</v>
       </c>
       <c r="N975">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="O975">
         <v>0</v>
@@ -89061,7 +89061,7 @@
         <v>0</v>
       </c>
       <c r="N976">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O976">
         <v>0</v>
@@ -89140,7 +89140,7 @@
         <v>0</v>
       </c>
       <c r="N977">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O977">
         <v>0</v>
@@ -89219,7 +89219,7 @@
         <v>0</v>
       </c>
       <c r="N978">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O978">
         <v>0</v>
@@ -89298,7 +89298,7 @@
         <v>0</v>
       </c>
       <c r="N979">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O979">
         <v>0</v>
@@ -89377,7 +89377,7 @@
         <v>0</v>
       </c>
       <c r="N980">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O980">
         <v>0</v>
@@ -89456,7 +89456,7 @@
         <v>0</v>
       </c>
       <c r="N981">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O981">
         <v>0</v>
@@ -89535,7 +89535,7 @@
         <v>0</v>
       </c>
       <c r="N982">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O982">
         <v>0</v>
@@ -89696,7 +89696,7 @@
         <v>0</v>
       </c>
       <c r="O984">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P984">
         <v>0</v>
@@ -89772,7 +89772,7 @@
         <v>0</v>
       </c>
       <c r="O985">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P985">
         <v>0</v>
@@ -89848,7 +89848,7 @@
         <v>0</v>
       </c>
       <c r="O986">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P986">
         <v>0</v>
@@ -89924,7 +89924,7 @@
         <v>0</v>
       </c>
       <c r="N987">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O987">
         <v>0</v>
@@ -90085,7 +90085,7 @@
         <v>0</v>
       </c>
       <c r="O989">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P989">
         <v>0</v>
@@ -90161,10 +90161,10 @@
         <v>0</v>
       </c>
       <c r="O990">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="P990">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q990">
         <v>0</v>
@@ -90240,7 +90240,7 @@
         <v>0</v>
       </c>
       <c r="O991">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P991">
         <v>0</v>
@@ -90319,7 +90319,7 @@
         <v>0</v>
       </c>
       <c r="O992">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P992">
         <v>0</v>
@@ -90398,7 +90398,7 @@
         <v>0</v>
       </c>
       <c r="O993">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P993">
         <v>0</v>
@@ -90471,10 +90471,10 @@
         <v>0</v>
       </c>
       <c r="N994">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O994">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P994">
         <v>0</v>
@@ -90553,7 +90553,7 @@
         <v>0</v>
       </c>
       <c r="O995">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P995">
         <v>0</v>
@@ -90629,10 +90629,10 @@
         <v>0</v>
       </c>
       <c r="N996">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O996">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P996">
         <v>0</v>
@@ -90708,10 +90708,10 @@
         <v>0</v>
       </c>
       <c r="N997">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O997">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P997">
         <v>0</v>
@@ -90790,7 +90790,7 @@
         <v>0</v>
       </c>
       <c r="O998">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P998">
         <v>0</v>
@@ -90869,7 +90869,7 @@
         <v>0</v>
       </c>
       <c r="O999">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P999">
         <v>0</v>
@@ -90948,7 +90948,7 @@
         <v>0</v>
       </c>
       <c r="O1000">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1000">
         <v>0</v>
@@ -91027,7 +91027,7 @@
         <v>0</v>
       </c>
       <c r="O1001">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1001">
         <v>0</v>
@@ -91185,7 +91185,7 @@
         <v>0</v>
       </c>
       <c r="O1003">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P1003">
         <v>0</v>
@@ -91264,7 +91264,7 @@
         <v>0</v>
       </c>
       <c r="O1004">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P1004">
         <v>0</v>
@@ -91340,10 +91340,10 @@
         <v>0</v>
       </c>
       <c r="N1005">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1005">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1005">
         <v>0</v>
@@ -91419,10 +91419,10 @@
         <v>0</v>
       </c>
       <c r="N1006">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1006">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1006">
         <v>0</v>
@@ -91498,10 +91498,10 @@
         <v>0</v>
       </c>
       <c r="N1007">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1007">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1007">
         <v>0</v>
@@ -91580,7 +91580,7 @@
         <v>0</v>
       </c>
       <c r="O1008">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1008">
         <v>0</v>
@@ -91659,7 +91659,7 @@
         <v>0</v>
       </c>
       <c r="O1009">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1009">
         <v>0</v>
@@ -91738,7 +91738,7 @@
         <v>0</v>
       </c>
       <c r="O1010">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1010">
         <v>0</v>
@@ -91814,7 +91814,7 @@
         <v>0</v>
       </c>
       <c r="N1011">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O1011">
         <v>0</v>
@@ -91893,7 +91893,7 @@
         <v>0</v>
       </c>
       <c r="N1012">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O1012">
         <v>0</v>
@@ -91972,7 +91972,7 @@
         <v>0</v>
       </c>
       <c r="N1013">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1013">
         <v>0</v>
@@ -92051,7 +92051,7 @@
         <v>0</v>
       </c>
       <c r="N1014">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1014">
         <v>0</v>
@@ -92130,7 +92130,7 @@
         <v>0</v>
       </c>
       <c r="N1015">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1015">
         <v>0</v>
@@ -92209,7 +92209,7 @@
         <v>0</v>
       </c>
       <c r="N1016">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1016">
         <v>0</v>
@@ -92367,7 +92367,7 @@
         <v>0</v>
       </c>
       <c r="N1018">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O1018">
         <v>0</v>
@@ -92446,7 +92446,7 @@
         <v>0</v>
       </c>
       <c r="N1019">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O1019">
         <v>0</v>
@@ -92525,7 +92525,7 @@
         <v>0</v>
       </c>
       <c r="N1020">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O1020">
         <v>0</v>
@@ -92604,7 +92604,7 @@
         <v>0</v>
       </c>
       <c r="N1021">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O1021">
         <v>0</v>
@@ -92683,7 +92683,7 @@
         <v>0</v>
       </c>
       <c r="N1022">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O1022">
         <v>0</v>
@@ -92762,7 +92762,7 @@
         <v>0</v>
       </c>
       <c r="N1023">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O1023">
         <v>0</v>
@@ -92841,7 +92841,7 @@
         <v>0</v>
       </c>
       <c r="N1024">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1024">
         <v>0</v>
@@ -92920,7 +92920,7 @@
         <v>0</v>
       </c>
       <c r="N1025">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1025">
         <v>0</v>
@@ -93078,10 +93078,10 @@
         <v>0</v>
       </c>
       <c r="N1027">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1027">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1027">
         <v>0</v>
@@ -93157,7 +93157,7 @@
         <v>0</v>
       </c>
       <c r="N1028">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1028">
         <v>0</v>
@@ -93236,7 +93236,7 @@
         <v>0</v>
       </c>
       <c r="N1029">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1029">
         <v>0</v>
@@ -93394,10 +93394,10 @@
         <v>0</v>
       </c>
       <c r="N1031">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O1031">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1031">
         <v>0</v>
@@ -93473,7 +93473,7 @@
         <v>0</v>
       </c>
       <c r="N1032">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O1032">
         <v>0</v>
@@ -93552,7 +93552,7 @@
         <v>0</v>
       </c>
       <c r="N1033">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1033">
         <v>0</v>
@@ -93710,7 +93710,7 @@
         <v>0</v>
       </c>
       <c r="N1035">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O1035">
         <v>0</v>
@@ -93789,7 +93789,7 @@
         <v>0</v>
       </c>
       <c r="N1036">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O1036">
         <v>0</v>
@@ -93868,7 +93868,7 @@
         <v>0</v>
       </c>
       <c r="N1037">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O1037">
         <v>0</v>
@@ -93947,7 +93947,7 @@
         <v>0</v>
       </c>
       <c r="N1038">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O1038">
         <v>0</v>
@@ -94026,7 +94026,7 @@
         <v>0</v>
       </c>
       <c r="N1039">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O1039">
         <v>0</v>
@@ -94105,7 +94105,7 @@
         <v>0</v>
       </c>
       <c r="N1040">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1040">
         <v>0</v>
@@ -94184,7 +94184,7 @@
         <v>0</v>
       </c>
       <c r="N1041">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1041">
         <v>0</v>
@@ -94263,7 +94263,7 @@
         <v>0</v>
       </c>
       <c r="N1042">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1042">
         <v>0</v>
@@ -94421,10 +94421,10 @@
         <v>0</v>
       </c>
       <c r="N1044">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="O1044">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P1044">
         <v>0</v>
@@ -94497,10 +94497,10 @@
         <v>0</v>
       </c>
       <c r="N1045">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="O1045">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P1045">
         <v>0</v>
@@ -94573,7 +94573,7 @@
         <v>0</v>
       </c>
       <c r="N1046">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="O1046">
         <v>0</v>
@@ -94652,10 +94652,10 @@
         <v>0</v>
       </c>
       <c r="N1047">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O1047">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P1047">
         <v>0</v>
@@ -94728,10 +94728,10 @@
         <v>0</v>
       </c>
       <c r="N1048">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="O1048">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P1048">
         <v>0</v>
@@ -94807,10 +94807,10 @@
         <v>0</v>
       </c>
       <c r="N1049">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O1049">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1049">
         <v>0</v>
@@ -94886,7 +94886,7 @@
         <v>0</v>
       </c>
       <c r="N1050">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="O1050">
         <v>0</v>
@@ -94965,10 +94965,10 @@
         <v>0</v>
       </c>
       <c r="N1051">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O1051">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1051">
         <v>0</v>
@@ -95044,7 +95044,7 @@
         <v>0</v>
       </c>
       <c r="N1052">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="O1052">
         <v>0</v>
@@ -95123,10 +95123,10 @@
         <v>0</v>
       </c>
       <c r="N1053">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="O1053">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1053">
         <v>0</v>
@@ -95199,10 +95199,10 @@
         <v>0</v>
       </c>
       <c r="N1054">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="O1054">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P1054">
         <v>0</v>
@@ -95278,10 +95278,10 @@
         <v>0</v>
       </c>
       <c r="N1055">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="O1055">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P1055">
         <v>0</v>
@@ -95357,10 +95357,10 @@
         <v>0</v>
       </c>
       <c r="N1056">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="O1056">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P1056">
         <v>0</v>
@@ -95433,10 +95433,10 @@
         <v>0</v>
       </c>
       <c r="N1057">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="O1057">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P1057">
         <v>0</v>
@@ -95512,10 +95512,10 @@
         <v>0</v>
       </c>
       <c r="N1058">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="O1058">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P1058">
         <v>0</v>
@@ -95591,7 +95591,7 @@
         <v>0</v>
       </c>
       <c r="N1059">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="O1059">
         <v>0</v>
@@ -95667,10 +95667,10 @@
         <v>0</v>
       </c>
       <c r="N1060">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="O1060">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1060">
         <v>0</v>
@@ -95746,7 +95746,7 @@
         <v>0</v>
       </c>
       <c r="O1061">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1061">
         <v>0</v>
@@ -95980,10 +95980,10 @@
         <v>0</v>
       </c>
       <c r="N1064">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1064">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1064">
         <v>0</v>
@@ -96062,7 +96062,7 @@
         <v>0</v>
       </c>
       <c r="O1065">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1065">
         <v>0</v>
@@ -96141,10 +96141,10 @@
         <v>0</v>
       </c>
       <c r="O1066">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1066">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q1066">
         <v>0</v>
@@ -96220,7 +96220,7 @@
         <v>0</v>
       </c>
       <c r="O1067">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1067">
         <v>0</v>
@@ -96533,7 +96533,7 @@
         <v>0</v>
       </c>
       <c r="N1071">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1071">
         <v>0</v>
@@ -96691,7 +96691,7 @@
         <v>0</v>
       </c>
       <c r="N1073">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1073">
         <v>0</v>
@@ -97089,7 +97089,7 @@
         <v>0</v>
       </c>
       <c r="N1078">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O1078">
         <v>0</v>
@@ -97171,7 +97171,7 @@
         <v>0</v>
       </c>
       <c r="N1079">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O1079">
         <v>0</v>
@@ -97250,7 +97250,7 @@
         <v>0</v>
       </c>
       <c r="N1080">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O1080">
         <v>0</v>
@@ -97329,7 +97329,7 @@
         <v>0</v>
       </c>
       <c r="N1081">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O1081">
         <v>0</v>
@@ -97408,7 +97408,7 @@
         <v>0</v>
       </c>
       <c r="N1082">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O1082">
         <v>0</v>
@@ -97487,7 +97487,7 @@
         <v>0</v>
       </c>
       <c r="N1083">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1083">
         <v>0</v>
@@ -97803,7 +97803,7 @@
         <v>0</v>
       </c>
       <c r="N1087">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1087">
         <v>0</v>
@@ -97964,7 +97964,7 @@
         <v>0</v>
       </c>
       <c r="O1089">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1089">
         <v>0</v>
@@ -98125,7 +98125,7 @@
         <v>0</v>
       </c>
       <c r="O1091">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="P1091">
         <v>0</v>
@@ -98204,7 +98204,7 @@
         <v>0</v>
       </c>
       <c r="O1092">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="P1092">
         <v>0</v>
@@ -98280,7 +98280,7 @@
         <v>0</v>
       </c>
       <c r="O1093">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P1093">
         <v>0</v>

--- a/0_SELECT_ZIVE_DATA_2023/visi_zive_irasai_atrankai._modif_v1 - Darb.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/visi_zive_irasai_atrankai._modif_v1 - Darb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAE41E2-0034-44A6-A655-FDFB64D7DDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86BCE4D-F976-4741-AE16-6B5ACA147319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9714" uniqueCount="3842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9680" uniqueCount="3840">
   <si>
     <t>filename</t>
   </si>
@@ -11542,12 +11542,6 @@
   </si>
   <si>
     <t>h_nz_len</t>
-  </si>
-  <si>
-    <t>J,N</t>
-  </si>
-  <si>
-    <t>Ž,N</t>
   </si>
   <si>
     <t>notes</t>
@@ -11591,7 +11585,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11619,6 +11613,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -11659,7 +11665,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -11692,6 +11698,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -12043,7 +12055,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3839</v>
+        <v>3837</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -12079,7 +12091,7 @@
         <v>3835</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>3840</v>
+        <v>3838</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>3827</v>
@@ -12088,7 +12100,7 @@
         <v>3828</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>3841</v>
+        <v>3839</v>
       </c>
       <c r="W1" s="13" t="s">
         <v>3816</v>
@@ -12100,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>3838</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
@@ -12730,7 +12742,7 @@
       <c r="B10">
         <v>128000</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>2714</v>
       </c>
       <c r="D10">
@@ -12878,7 +12890,7 @@
       <c r="B12">
         <v>128000</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>2710</v>
       </c>
       <c r="D12">
@@ -12889,9 +12901,6 @@
       </c>
       <c r="F12">
         <v>1111</v>
-      </c>
-      <c r="G12" t="s">
-        <v>3836</v>
       </c>
       <c r="H12" t="s">
         <v>3795</v>
@@ -13568,7 +13577,7 @@
       <c r="B21">
         <v>127999</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="16" t="s">
         <v>2718</v>
       </c>
       <c r="D21">
@@ -13579,9 +13588,6 @@
       </c>
       <c r="F21">
         <v>1111</v>
-      </c>
-      <c r="G21" t="s">
-        <v>3836</v>
       </c>
       <c r="H21" t="s">
         <v>3795</v>
@@ -13796,7 +13802,7 @@
       <c r="B24">
         <v>127999</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="16" t="s">
         <v>2736</v>
       </c>
       <c r="D24">
@@ -13807,9 +13813,6 @@
       </c>
       <c r="F24">
         <v>1111</v>
-      </c>
-      <c r="G24" t="s">
-        <v>3836</v>
       </c>
       <c r="H24" t="s">
         <v>3795</v>
@@ -14717,7 +14720,7 @@
       <c r="B36">
         <v>127999</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="16" t="s">
         <v>2711</v>
       </c>
       <c r="D36">
@@ -14728,9 +14731,6 @@
       </c>
       <c r="F36">
         <v>1111</v>
-      </c>
-      <c r="G36" t="s">
-        <v>3836</v>
       </c>
       <c r="H36" t="s">
         <v>3795</v>
@@ -15253,7 +15253,7 @@
       <c r="B43">
         <v>127999</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="16" t="s">
         <v>2712</v>
       </c>
       <c r="D43">
@@ -15264,9 +15264,6 @@
       </c>
       <c r="F43">
         <v>1111</v>
-      </c>
-      <c r="G43" t="s">
-        <v>3836</v>
       </c>
       <c r="H43" t="s">
         <v>3801</v>
@@ -15564,7 +15561,7 @@
       <c r="B47">
         <v>127999</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="16" t="s">
         <v>2754</v>
       </c>
       <c r="D47">
@@ -15575,9 +15572,6 @@
       </c>
       <c r="F47">
         <v>1111</v>
-      </c>
-      <c r="G47" t="s">
-        <v>3836</v>
       </c>
       <c r="H47" t="s">
         <v>3795</v>
@@ -15644,7 +15638,7 @@
       <c r="B48">
         <v>127999</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="16" t="s">
         <v>2755</v>
       </c>
       <c r="D48">
@@ -15655,9 +15649,6 @@
       </c>
       <c r="F48">
         <v>1111</v>
-      </c>
-      <c r="G48" t="s">
-        <v>3837</v>
       </c>
       <c r="H48" t="s">
         <v>3795</v>
@@ -15955,7 +15946,7 @@
       <c r="B52">
         <v>127999</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="16" t="s">
         <v>2767</v>
       </c>
       <c r="D52">
@@ -15966,9 +15957,6 @@
       </c>
       <c r="F52">
         <v>1111</v>
-      </c>
-      <c r="G52" t="s">
-        <v>3837</v>
       </c>
       <c r="H52" t="s">
         <v>3795</v>
@@ -17871,7 +17859,7 @@
       <c r="B77">
         <v>127999</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="16" t="s">
         <v>2792</v>
       </c>
       <c r="D77">
@@ -17882,9 +17870,6 @@
       </c>
       <c r="F77">
         <v>1111</v>
-      </c>
-      <c r="G77" t="s">
-        <v>3837</v>
       </c>
       <c r="H77" t="s">
         <v>3795</v>
@@ -17951,7 +17936,7 @@
       <c r="B78">
         <v>127999</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="C78" s="16" t="s">
         <v>2793</v>
       </c>
       <c r="D78">
@@ -17962,9 +17947,6 @@
       </c>
       <c r="F78">
         <v>1111</v>
-      </c>
-      <c r="G78" t="s">
-        <v>3837</v>
       </c>
       <c r="H78" t="s">
         <v>3795</v>
@@ -19802,7 +19784,7 @@
       <c r="B102">
         <v>127999</v>
       </c>
-      <c r="C102" s="15" t="s">
+      <c r="C102" s="16" t="s">
         <v>2809</v>
       </c>
       <c r="D102">
@@ -19813,9 +19795,6 @@
       </c>
       <c r="F102">
         <v>1111</v>
-      </c>
-      <c r="G102" t="s">
-        <v>3836</v>
       </c>
       <c r="H102" t="s">
         <v>3795</v>
@@ -19959,7 +19938,7 @@
       <c r="B104">
         <v>127999</v>
       </c>
-      <c r="C104" s="15" t="s">
+      <c r="C104" s="17" t="s">
         <v>2811</v>
       </c>
       <c r="D104">
@@ -19970,9 +19949,6 @@
       </c>
       <c r="F104">
         <v>1111</v>
-      </c>
-      <c r="G104" t="s">
-        <v>3836</v>
       </c>
       <c r="H104" t="s">
         <v>3795</v>
@@ -20039,7 +20015,7 @@
       <c r="B105">
         <v>127999</v>
       </c>
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="16" t="s">
         <v>2812</v>
       </c>
       <c r="D105">
@@ -20050,9 +20026,6 @@
       </c>
       <c r="F105">
         <v>1111</v>
-      </c>
-      <c r="G105" t="s">
-        <v>3836</v>
       </c>
       <c r="H105" t="s">
         <v>3795</v>
@@ -20812,7 +20785,7 @@
       <c r="B115">
         <v>127999</v>
       </c>
-      <c r="C115" s="15" t="s">
+      <c r="C115" s="16" t="s">
         <v>2830</v>
       </c>
       <c r="D115">
@@ -20823,9 +20796,6 @@
       </c>
       <c r="F115">
         <v>1111</v>
-      </c>
-      <c r="G115" t="s">
-        <v>3836</v>
       </c>
       <c r="H115" t="s">
         <v>3795</v>
@@ -20892,7 +20862,7 @@
       <c r="B116">
         <v>127999</v>
       </c>
-      <c r="C116" s="15" t="s">
+      <c r="C116" s="16" t="s">
         <v>2831</v>
       </c>
       <c r="D116">
@@ -20903,9 +20873,6 @@
       </c>
       <c r="F116">
         <v>1111</v>
-      </c>
-      <c r="G116" t="s">
-        <v>3836</v>
       </c>
       <c r="H116" t="s">
         <v>3795</v>
@@ -23664,7 +23631,7 @@
       <c r="B152">
         <v>127999</v>
       </c>
-      <c r="C152" s="15" t="s">
+      <c r="C152" s="16" t="s">
         <v>2859</v>
       </c>
       <c r="D152">
@@ -23675,9 +23642,6 @@
       </c>
       <c r="F152">
         <v>1111</v>
-      </c>
-      <c r="G152" t="s">
-        <v>3836</v>
       </c>
       <c r="H152" t="s">
         <v>3798</v>
@@ -24357,7 +24321,7 @@
       <c r="B161">
         <v>127999</v>
       </c>
-      <c r="C161" s="15" t="s">
+      <c r="C161" s="16" t="s">
         <v>2876</v>
       </c>
       <c r="D161">
@@ -24368,9 +24332,6 @@
       </c>
       <c r="F161">
         <v>1111</v>
-      </c>
-      <c r="G161" t="s">
-        <v>3837</v>
       </c>
       <c r="H161" t="s">
         <v>3798</v>
@@ -28817,7 +28778,7 @@
       <c r="B219">
         <v>127999</v>
       </c>
-      <c r="C219" s="15" t="s">
+      <c r="C219" s="16" t="s">
         <v>2926</v>
       </c>
       <c r="D219">
@@ -28828,9 +28789,6 @@
       </c>
       <c r="F219">
         <v>1111</v>
-      </c>
-      <c r="G219" t="s">
-        <v>3836</v>
       </c>
       <c r="H219" t="s">
         <v>3798</v>
@@ -29359,7 +29317,7 @@
       <c r="B226">
         <v>127999</v>
       </c>
-      <c r="C226" s="15" t="s">
+      <c r="C226" s="16" t="s">
         <v>2933</v>
       </c>
       <c r="D226">
@@ -29370,9 +29328,6 @@
       </c>
       <c r="F226">
         <v>1111</v>
-      </c>
-      <c r="G226" t="s">
-        <v>3836</v>
       </c>
       <c r="H226" t="s">
         <v>3798</v>
@@ -29439,7 +29394,7 @@
       <c r="B227">
         <v>127999</v>
       </c>
-      <c r="C227" s="15" t="s">
+      <c r="C227" s="16" t="s">
         <v>2934</v>
       </c>
       <c r="D227">
@@ -29450,9 +29405,6 @@
       </c>
       <c r="F227">
         <v>1111</v>
-      </c>
-      <c r="G227" t="s">
-        <v>3836</v>
       </c>
       <c r="H227" t="s">
         <v>3798</v>
@@ -29596,7 +29548,7 @@
       <c r="B229">
         <v>127999</v>
       </c>
-      <c r="C229" s="15" t="s">
+      <c r="C229" s="16" t="s">
         <v>2936</v>
       </c>
       <c r="D229">
@@ -29607,9 +29559,6 @@
       </c>
       <c r="F229">
         <v>1111</v>
-      </c>
-      <c r="G229" t="s">
-        <v>3836</v>
       </c>
       <c r="H229" t="s">
         <v>3798</v>
@@ -29676,7 +29625,7 @@
       <c r="B230">
         <v>127999</v>
       </c>
-      <c r="C230" s="15" t="s">
+      <c r="C230" s="16" t="s">
         <v>2937</v>
       </c>
       <c r="D230">
@@ -29687,9 +29636,6 @@
       </c>
       <c r="F230">
         <v>1111</v>
-      </c>
-      <c r="G230" t="s">
-        <v>3836</v>
       </c>
       <c r="H230" t="s">
         <v>3798</v>
@@ -40453,7 +40399,7 @@
       <c r="B370">
         <v>127999</v>
       </c>
-      <c r="C370" s="15" t="s">
+      <c r="C370" s="16" t="s">
         <v>3077</v>
       </c>
       <c r="D370">
@@ -40464,9 +40410,6 @@
       </c>
       <c r="F370">
         <v>1111</v>
-      </c>
-      <c r="G370" t="s">
-        <v>3836</v>
       </c>
       <c r="H370" t="s">
         <v>3798</v>
@@ -40533,7 +40476,7 @@
       <c r="B371">
         <v>127999</v>
       </c>
-      <c r="C371" s="15" t="s">
+      <c r="C371" s="16" t="s">
         <v>3078</v>
       </c>
       <c r="D371">
@@ -40544,9 +40487,6 @@
       </c>
       <c r="F371">
         <v>1111</v>
-      </c>
-      <c r="G371" t="s">
-        <v>3836</v>
       </c>
       <c r="H371" t="s">
         <v>3798</v>
@@ -40690,7 +40630,7 @@
       <c r="B373">
         <v>127999</v>
       </c>
-      <c r="C373" s="15" t="s">
+      <c r="C373" s="16" t="s">
         <v>3080</v>
       </c>
       <c r="D373">
@@ -40701,9 +40641,6 @@
       </c>
       <c r="F373">
         <v>1111</v>
-      </c>
-      <c r="G373" t="s">
-        <v>3837</v>
       </c>
       <c r="H373" t="s">
         <v>3798</v>
@@ -41078,7 +41015,7 @@
       <c r="B378">
         <v>127999</v>
       </c>
-      <c r="C378" s="15" t="s">
+      <c r="C378" s="16" t="s">
         <v>3085</v>
       </c>
       <c r="D378">
@@ -41089,9 +41026,6 @@
       </c>
       <c r="F378">
         <v>1111</v>
-      </c>
-      <c r="G378" t="s">
-        <v>3836</v>
       </c>
       <c r="H378" t="s">
         <v>3798</v>
@@ -41617,7 +41551,7 @@
       <c r="B385">
         <v>127999</v>
       </c>
-      <c r="C385" s="15" t="s">
+      <c r="C385" s="16" t="s">
         <v>3089</v>
       </c>
       <c r="D385">
@@ -41628,9 +41562,6 @@
       </c>
       <c r="F385">
         <v>1111</v>
-      </c>
-      <c r="G385" t="s">
-        <v>3836</v>
       </c>
       <c r="H385" t="s">
         <v>3798</v>
@@ -42079,7 +42010,7 @@
       <c r="B391">
         <v>127999</v>
       </c>
-      <c r="C391" s="15" t="s">
+      <c r="C391" s="16" t="s">
         <v>3098</v>
       </c>
       <c r="D391">
@@ -42090,9 +42021,6 @@
       </c>
       <c r="F391">
         <v>1111</v>
-      </c>
-      <c r="G391" t="s">
-        <v>3836</v>
       </c>
       <c r="H391" t="s">
         <v>3798</v>
@@ -42544,7 +42472,7 @@
       <c r="B397">
         <v>127999</v>
       </c>
-      <c r="C397" s="15" t="s">
+      <c r="C397" s="16" t="s">
         <v>3104</v>
       </c>
       <c r="D397">
@@ -42555,9 +42483,6 @@
       </c>
       <c r="F397">
         <v>1111</v>
-      </c>
-      <c r="G397" t="s">
-        <v>3836</v>
       </c>
       <c r="H397" t="s">
         <v>3798</v>
@@ -42778,7 +42703,7 @@
       <c r="B400">
         <v>127999</v>
       </c>
-      <c r="C400" s="15" t="s">
+      <c r="C400" s="16" t="s">
         <v>3107</v>
       </c>
       <c r="D400">
@@ -42789,9 +42714,6 @@
       </c>
       <c r="F400">
         <v>1111</v>
-      </c>
-      <c r="G400" t="s">
-        <v>3836</v>
       </c>
       <c r="H400" t="s">
         <v>3798</v>
@@ -94796,7 +94718,7 @@
       <c r="B1077">
         <v>127999</v>
       </c>
-      <c r="C1077" s="15" t="s">
+      <c r="C1077" s="16" t="s">
         <v>3782</v>
       </c>
       <c r="D1077">
@@ -94807,9 +94729,6 @@
       </c>
       <c r="F1077">
         <v>1111</v>
-      </c>
-      <c r="G1077" t="s">
-        <v>3836</v>
       </c>
       <c r="H1077" t="s">
         <v>3795</v>
@@ -94876,7 +94795,7 @@
       <c r="B1078">
         <v>127999</v>
       </c>
-      <c r="C1078" s="15" t="s">
+      <c r="C1078" s="16" t="s">
         <v>3783</v>
       </c>
       <c r="D1078">
@@ -94887,9 +94806,6 @@
       </c>
       <c r="F1078">
         <v>1111</v>
-      </c>
-      <c r="G1078" t="s">
-        <v>3836</v>
       </c>
       <c r="H1078" t="s">
         <v>3795</v>
@@ -95803,7 +95719,7 @@
       <c r="B1090">
         <v>128000</v>
       </c>
-      <c r="C1090" s="15" t="s">
+      <c r="C1090" s="16" t="s">
         <v>2707</v>
       </c>
       <c r="D1090">
@@ -95814,9 +95730,6 @@
       </c>
       <c r="F1090">
         <v>1111</v>
-      </c>
-      <c r="G1090" t="s">
-        <v>3836</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -95880,7 +95793,7 @@
       <c r="B1091">
         <v>128000</v>
       </c>
-      <c r="C1091" s="15" t="s">
+      <c r="C1091" s="16" t="s">
         <v>2709</v>
       </c>
       <c r="D1091">
@@ -95891,9 +95804,6 @@
       </c>
       <c r="F1091">
         <v>1111</v>
-      </c>
-      <c r="G1091" t="s">
-        <v>3836</v>
       </c>
       <c r="H1091" t="s">
         <v>3802</v>

--- a/0_SELECT_ZIVE_DATA_2023/visi_zive_irasai_atrankai._modif_v1 - Darb.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/visi_zive_irasai_atrankai._modif_v1 - Darb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55008FA5-5F64-4400-94B8-C48AD83C302A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CE5D1E-D4F1-4566-9FF1-E87EE3290C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14819,7 +14819,7 @@
         <v>4</v>
       </c>
       <c r="F38">
-        <v>3333</v>
+        <v>2222</v>
       </c>
       <c r="H38" t="s">
         <v>3768</v>
@@ -14896,7 +14896,7 @@
         <v>6</v>
       </c>
       <c r="F39">
-        <v>3333</v>
+        <v>2222</v>
       </c>
       <c r="H39" t="s">
         <v>3768</v>
@@ -44577,7 +44577,7 @@
         <v>9</v>
       </c>
       <c r="F425">
-        <v>1111</v>
+        <v>2222</v>
       </c>
       <c r="H425" t="s">
         <v>3769</v>

--- a/0_SELECT_ZIVE_DATA_2023/visi_zive_irasai_atrankai._modif_v1 - Darb.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/visi_zive_irasai_atrankai._modif_v1 - Darb.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FC6BF6-E146-4ABB-A951-ACCC096CEF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDDD84A-8489-4CE0-92C7-AFA47265EF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="1140" windowWidth="18600" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9631" uniqueCount="3822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9631" uniqueCount="3825">
   <si>
     <t>filename</t>
   </si>
@@ -11500,6 +11500,15 @@
   </si>
   <si>
     <t>tp%</t>
+  </si>
+  <si>
+    <t>Pažymėti tag = 11110 , kurie yra pretendentai  mokymui, bus patvrtinta po anotavimo</t>
+  </si>
+  <si>
+    <t>Pažymėti tag = 22220 , kurie yra pretendentai  testavimui, bus patvrtinta po anotavimo</t>
+  </si>
+  <si>
+    <t>Pažymėti tag = 33330, gana daug triukšmų, gali pretenduoti triukšmų testavimui, bus patvirtinta po anotavimo</t>
   </si>
 </sst>
 </file>
@@ -17675,8 +17684,8 @@
       <c r="E65" t="s">
         <v>9</v>
       </c>
-      <c r="F65" t="s">
-        <v>9</v>
+      <c r="F65">
+        <v>11110</v>
       </c>
       <c r="H65" t="s">
         <v>9</v>
@@ -30651,8 +30660,8 @@
       <c r="E211" t="s">
         <v>9</v>
       </c>
-      <c r="F211" t="s">
-        <v>9</v>
+      <c r="F211">
+        <v>11110</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -32591,7 +32600,7 @@
       </c>
     </row>
     <row r="233" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A233" s="3" t="s">
+      <c r="A233" t="s">
         <v>822</v>
       </c>
       <c r="B233">
@@ -32606,8 +32615,8 @@
       <c r="E233" t="s">
         <v>9</v>
       </c>
-      <c r="F233" t="s">
-        <v>9</v>
+      <c r="F233">
+        <v>11110</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -32618,19 +32627,19 @@
       <c r="J233" s="10">
         <v>511</v>
       </c>
-      <c r="K233" s="19">
-        <v>0</v>
-      </c>
-      <c r="L233" s="18">
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
         <v>3</v>
       </c>
       <c r="M233">
         <v>0</v>
       </c>
-      <c r="N233" s="19">
-        <v>0</v>
-      </c>
-      <c r="O233" s="18">
+      <c r="N233">
+        <v>0</v>
+      </c>
+      <c r="O233">
         <v>0</v>
       </c>
       <c r="P233">
@@ -108475,59 +108484,74 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6740BA52-0B9E-43BD-B693-6B53C9B815B0}">
-  <dimension ref="B2:C15"/>
+  <dimension ref="B2:C18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="5" t="s">
         <v>3779</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B3" s="5"/>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B4" s="5" t="s">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
+        <v>3822</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="5" t="s">
         <v>3810</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B5" s="5"/>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B8" s="5" t="s">
         <v>3809</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B7" s="5"/>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B8" s="5" t="s">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B9" s="5" t="s">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="5"/>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="5" t="s">
         <v>3780</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B9" s="5"/>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B10" s="5" t="s">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="5"/>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="5" t="s">
         <v>3781</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B11" s="5"/>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B12" s="5" t="s">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="5"/>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B15" s="5" t="s">
         <v>3782</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
         <v>3783</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C18" t="s">
         <v>3784</v>
       </c>
     </row>
